--- a/research/traditional_assets/database/data/isle_of_man/isle_of_man_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/isle_of_man/isle_of_man_metals_mining.xlsx
@@ -1341,43 +1341,43 @@
         <v>24.4587155963303</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>474.928208526618</v>
       </c>
       <c r="G2">
         <v>0.4</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0405818181818182</v>
       </c>
       <c r="I2">
         <v>0.0985663082437276</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>100.6</v>
       </c>
       <c r="L2">
-        <v>113.09327394611</v>
+        <v>111.938696994615</v>
       </c>
       <c r="M2">
         <v>97.3</v>
       </c>
       <c r="N2">
-        <v>98.7932739461105</v>
+        <v>98.7546969946153</v>
       </c>
       <c r="O2">
         <v>11</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.116</v>
       </c>
       <c r="Q2">
         <v>0.0980618365453215</v>
       </c>
       <c r="R2">
-        <v>0.0962938904585125</v>
+        <v>0.0963388904585125</v>
       </c>
       <c r="S2">
         <v>0.06373661666253411</v>
@@ -1399,13 +1399,13 @@
         <v>0.101815091204473</v>
       </c>
       <c r="X2">
-        <v>0.0962938904585125</v>
+        <v>0.0968039297560733</v>
       </c>
       <c r="Y2">
         <v>1.09183838840961</v>
       </c>
       <c r="Z2">
-        <v>0.984219909265296</v>
+        <v>0.9941615245104</v>
       </c>
       <c r="AA2">
         <v>11</v>
@@ -1486,7 +1486,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1623,22 +1623,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09629389045851253</v>
+        <v>0.09633889045851254</v>
       </c>
       <c r="C2">
-        <v>113.0932739461105</v>
+        <v>111.9386969946153</v>
       </c>
       <c r="D2">
-        <v>98.79327394611049</v>
+        <v>98.75469699461529</v>
       </c>
       <c r="E2">
-        <v>-11</v>
+        <v>-9.884</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.116</v>
       </c>
       <c r="G2">
         <v>14.3</v>
@@ -1659,28 +1659,28 @@
         <v>26.66</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.05613479999999999</v>
       </c>
       <c r="N2">
-        <v>26.66</v>
+        <v>26.6038652</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>26.66</v>
+        <v>26.6038652</v>
       </c>
       <c r="Q2">
-        <v>27.5</v>
+        <v>27.4438652</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09629389045851253</v>
+        <v>0.09680392975607327</v>
       </c>
       <c r="T2">
-        <v>0.9842199092652959</v>
+        <v>0.9941615245104</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>474.9282085266182</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1705,22 +1705,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09633889045851254</v>
+        <v>0.09638389045851251</v>
       </c>
       <c r="C3">
-        <v>111.9386969946153</v>
+        <v>110.7841501585368</v>
       </c>
       <c r="D3">
-        <v>98.75469699461529</v>
+        <v>98.71615015853683</v>
       </c>
       <c r="E3">
-        <v>-9.884</v>
+        <v>-8.768000000000001</v>
       </c>
       <c r="F3">
-        <v>1.116</v>
+        <v>2.232</v>
       </c>
       <c r="G3">
         <v>14.3</v>
@@ -1741,28 +1741,28 @@
         <v>26.66</v>
       </c>
       <c r="M3">
-        <v>0.05613479999999999</v>
+        <v>0.1122696</v>
       </c>
       <c r="N3">
-        <v>26.6038652</v>
+        <v>26.5477304</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>26.6038652</v>
+        <v>26.5477304</v>
       </c>
       <c r="Q3">
-        <v>27.4438652</v>
+        <v>27.3877304</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09680392975607327</v>
+        <v>0.09732437801889032</v>
       </c>
       <c r="T3">
-        <v>0.9941615245104</v>
+        <v>1.004306029862547</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>474.9282085266182</v>
+        <v>237.4641042633091</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1787,22 +1787,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09638389045851251</v>
+        <v>0.09642889045851251</v>
       </c>
       <c r="C4">
-        <v>110.7841501585368</v>
+        <v>109.629633402624</v>
       </c>
       <c r="D4">
-        <v>98.71615015853683</v>
+        <v>98.67763340262402</v>
       </c>
       <c r="E4">
-        <v>-8.768000000000001</v>
+        <v>-7.652</v>
       </c>
       <c r="F4">
-        <v>2.232</v>
+        <v>3.348</v>
       </c>
       <c r="G4">
         <v>14.3</v>
@@ -1823,28 +1823,28 @@
         <v>26.66</v>
       </c>
       <c r="M4">
-        <v>0.1122696</v>
+        <v>0.1684044</v>
       </c>
       <c r="N4">
-        <v>26.5477304</v>
+        <v>26.4915956</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>26.5477304</v>
+        <v>26.4915956</v>
       </c>
       <c r="Q4">
-        <v>27.3877304</v>
+        <v>27.3315956</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09732437801889032</v>
+        <v>0.09785555717372424</v>
       </c>
       <c r="T4">
-        <v>1.004306029862547</v>
+        <v>1.014659700273501</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>237.4641042633091</v>
+        <v>158.3094028422061</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1869,22 +1869,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09642889045851251</v>
+        <v>0.09647389045851251</v>
       </c>
       <c r="C5">
-        <v>109.629633402624</v>
+        <v>108.4751466916809</v>
       </c>
       <c r="D5">
-        <v>98.67763340262402</v>
+        <v>98.63914669168091</v>
       </c>
       <c r="E5">
-        <v>-7.652</v>
+        <v>-6.536</v>
       </c>
       <c r="F5">
-        <v>3.348</v>
+        <v>4.464</v>
       </c>
       <c r="G5">
         <v>14.3</v>
@@ -1905,28 +1905,28 @@
         <v>26.66</v>
       </c>
       <c r="M5">
-        <v>0.1684044</v>
+        <v>0.2245392</v>
       </c>
       <c r="N5">
-        <v>26.4915956</v>
+        <v>26.4354608</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>26.4915956</v>
+        <v>26.4354608</v>
       </c>
       <c r="Q5">
-        <v>27.3315956</v>
+        <v>27.2754608</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09785555717372424</v>
+        <v>0.09839780256095054</v>
       </c>
       <c r="T5">
-        <v>1.014659700273501</v>
+        <v>1.02522907215135</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>158.3094028422061</v>
+        <v>118.7320521316545</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09647389045851251</v>
+        <v>0.09651889045851253</v>
       </c>
       <c r="C6">
-        <v>108.4751466916809</v>
+        <v>107.3206899905663</v>
       </c>
       <c r="D6">
-        <v>98.63914669168091</v>
+        <v>98.60068999056628</v>
       </c>
       <c r="E6">
-        <v>-6.536</v>
+        <v>-5.42</v>
       </c>
       <c r="F6">
-        <v>4.464</v>
+        <v>5.58</v>
       </c>
       <c r="G6">
         <v>14.3</v>
@@ -1987,28 +1987,28 @@
         <v>26.66</v>
       </c>
       <c r="M6">
-        <v>0.2245392</v>
+        <v>0.280674</v>
       </c>
       <c r="N6">
-        <v>26.4354608</v>
+        <v>26.379326</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>26.4354608</v>
+        <v>26.379326</v>
       </c>
       <c r="Q6">
-        <v>27.2754608</v>
+        <v>27.219326</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09839780256095054</v>
+        <v>0.0989514636405395</v>
       </c>
       <c r="T6">
-        <v>1.02522907215135</v>
+        <v>1.036020957121364</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>118.7320521316545</v>
+        <v>94.98564170532362</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2033,22 +2033,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09651889045851253</v>
+        <v>0.09656389045851253</v>
       </c>
       <c r="C7">
-        <v>107.3206899905663</v>
+        <v>106.1662632641939</v>
       </c>
       <c r="D7">
-        <v>98.60068999056628</v>
+        <v>98.56226326419387</v>
       </c>
       <c r="E7">
-        <v>-5.42</v>
+        <v>-4.303999999999999</v>
       </c>
       <c r="F7">
-        <v>5.58</v>
+        <v>6.696000000000001</v>
       </c>
       <c r="G7">
         <v>14.3</v>
@@ -2069,28 +2069,28 @@
         <v>26.66</v>
       </c>
       <c r="M7">
-        <v>0.280674</v>
+        <v>0.3368088</v>
       </c>
       <c r="N7">
-        <v>26.379326</v>
+        <v>26.3231912</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>26.379326</v>
+        <v>26.3231912</v>
       </c>
       <c r="Q7">
-        <v>27.219326</v>
+        <v>27.1631912</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0989514636405395</v>
+        <v>0.09951690474309843</v>
       </c>
       <c r="T7">
-        <v>1.036020957121364</v>
+        <v>1.047042456665208</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>94.98564170532362</v>
+        <v>79.15470142110301</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2115,22 +2115,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09656389045851252</v>
+        <v>0.09660889045851252</v>
       </c>
       <c r="C8">
-        <v>106.1662632641939</v>
+        <v>105.011866477532</v>
       </c>
       <c r="D8">
-        <v>98.56226326419389</v>
+        <v>98.523866477532</v>
       </c>
       <c r="E8">
-        <v>-4.304</v>
+        <v>-3.188000000000001</v>
       </c>
       <c r="F8">
-        <v>6.696</v>
+        <v>7.811999999999999</v>
       </c>
       <c r="G8">
         <v>14.3</v>
@@ -2151,28 +2151,28 @@
         <v>26.66</v>
       </c>
       <c r="M8">
-        <v>0.3368088</v>
+        <v>0.3929435999999999</v>
       </c>
       <c r="N8">
-        <v>26.3231912</v>
+        <v>26.2670564</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>26.3231912</v>
+        <v>26.2670564</v>
       </c>
       <c r="Q8">
-        <v>27.1631912</v>
+        <v>27.1070564</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09951690474309843</v>
+        <v>0.1000945058693683</v>
       </c>
       <c r="T8">
-        <v>1.047042456665208</v>
+        <v>1.058300977704619</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>79.15470142110303</v>
+        <v>67.84688693237403</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2197,22 +2197,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09660889045851251</v>
+        <v>0.09665389045851253</v>
       </c>
       <c r="C9">
-        <v>105.011866477532</v>
+        <v>103.8574995956035</v>
       </c>
       <c r="D9">
-        <v>98.523866477532</v>
+        <v>98.48549959560349</v>
       </c>
       <c r="E9">
-        <v>-3.188</v>
+        <v>-2.072000000000001</v>
       </c>
       <c r="F9">
-        <v>7.812</v>
+        <v>8.927999999999999</v>
       </c>
       <c r="G9">
         <v>14.3</v>
@@ -2233,28 +2233,28 @@
         <v>26.66</v>
       </c>
       <c r="M9">
-        <v>0.3929436</v>
+        <v>0.4490783999999999</v>
       </c>
       <c r="N9">
-        <v>26.2670564</v>
+        <v>26.2109216</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>26.2670564</v>
+        <v>26.2109216</v>
       </c>
       <c r="Q9">
-        <v>27.1070564</v>
+        <v>27.0509216</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1000945058693683</v>
+        <v>0.1006846635418614</v>
       </c>
       <c r="T9">
-        <v>1.058300977704619</v>
+        <v>1.069804249201409</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>67.84688693237402</v>
+        <v>59.36602606582726</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2279,22 +2279,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09665389045851253</v>
+        <v>0.09669889045851253</v>
       </c>
       <c r="C10">
-        <v>103.8574995956035</v>
+        <v>102.7031625834857</v>
       </c>
       <c r="D10">
-        <v>98.48549959560349</v>
+        <v>98.44716258348573</v>
       </c>
       <c r="E10">
-        <v>-2.072000000000001</v>
+        <v>-0.9560000000000013</v>
       </c>
       <c r="F10">
-        <v>8.927999999999999</v>
+        <v>10.044</v>
       </c>
       <c r="G10">
         <v>14.3</v>
@@ -2315,28 +2315,28 @@
         <v>26.66</v>
       </c>
       <c r="M10">
-        <v>0.4490783999999999</v>
+        <v>0.5052131999999999</v>
       </c>
       <c r="N10">
-        <v>26.2109216</v>
+        <v>26.1547868</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>26.2109216</v>
+        <v>26.1547868</v>
       </c>
       <c r="Q10">
-        <v>27.0509216</v>
+        <v>26.9947868</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1006846635418614</v>
+        <v>0.1012877917126511</v>
       </c>
       <c r="T10">
-        <v>1.069804249201409</v>
+        <v>1.081560339851974</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>59.36602606582726</v>
+        <v>52.76980094740202</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2361,22 +2361,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09669889045851253</v>
+        <v>0.09674389045851253</v>
       </c>
       <c r="C11">
-        <v>102.7031625834857</v>
+        <v>101.5488554063105</v>
       </c>
       <c r="D11">
-        <v>98.44716258348573</v>
+        <v>98.40885540631045</v>
       </c>
       <c r="E11">
-        <v>-0.9560000000000013</v>
+        <v>0.1599999999999984</v>
       </c>
       <c r="F11">
-        <v>10.044</v>
+        <v>11.16</v>
       </c>
       <c r="G11">
         <v>14.3</v>
@@ -2397,28 +2397,28 @@
         <v>26.66</v>
       </c>
       <c r="M11">
-        <v>0.5052131999999999</v>
+        <v>0.5613479999999998</v>
       </c>
       <c r="N11">
-        <v>26.1547868</v>
+        <v>26.098652</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>26.1547868</v>
+        <v>26.098652</v>
       </c>
       <c r="Q11">
-        <v>26.9947868</v>
+        <v>26.938652</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1012877917126511</v>
+        <v>0.1019043227316806</v>
       </c>
       <c r="T11">
-        <v>1.081560339851974</v>
+        <v>1.09357767696144</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>52.76980094740202</v>
+        <v>47.49282085266182</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2443,22 +2443,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09674389045851253</v>
+        <v>0.09678889045851251</v>
       </c>
       <c r="C12">
-        <v>101.5488554063105</v>
+        <v>100.3945780292636</v>
       </c>
       <c r="D12">
-        <v>98.40885540631045</v>
+        <v>98.3705780292636</v>
       </c>
       <c r="E12">
-        <v>0.1600000000000001</v>
+        <v>1.276</v>
       </c>
       <c r="F12">
-        <v>11.16</v>
+        <v>12.276</v>
       </c>
       <c r="G12">
         <v>14.3</v>
@@ -2479,28 +2479,28 @@
         <v>26.66</v>
       </c>
       <c r="M12">
-        <v>0.561348</v>
+        <v>0.6174828</v>
       </c>
       <c r="N12">
-        <v>26.098652</v>
+        <v>26.0425172</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>26.098652</v>
+        <v>26.0425172</v>
       </c>
       <c r="Q12">
-        <v>26.938652</v>
+        <v>26.8825172</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1019043227316806</v>
+        <v>0.1025347083803511</v>
       </c>
       <c r="T12">
-        <v>1.09357767696144</v>
+        <v>1.10586506659022</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>47.49282085266181</v>
+        <v>43.175291684238</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2525,22 +2525,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09678889045851251</v>
+        <v>0.09683389045851253</v>
       </c>
       <c r="C13">
-        <v>100.3945780292636</v>
+        <v>99.24033041758526</v>
       </c>
       <c r="D13">
-        <v>98.3705780292636</v>
+        <v>98.33233041758525</v>
       </c>
       <c r="E13">
-        <v>1.276</v>
+        <v>2.391999999999999</v>
       </c>
       <c r="F13">
-        <v>12.276</v>
+        <v>13.392</v>
       </c>
       <c r="G13">
         <v>14.3</v>
@@ -2561,28 +2561,28 @@
         <v>26.66</v>
       </c>
       <c r="M13">
-        <v>0.6174828</v>
+        <v>0.6736175999999999</v>
       </c>
       <c r="N13">
-        <v>26.0425172</v>
+        <v>25.9863824</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>26.0425172</v>
+        <v>25.9863824</v>
       </c>
       <c r="Q13">
-        <v>26.8825172</v>
+        <v>26.8263824</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1025347083803511</v>
+        <v>0.1031794209755824</v>
       </c>
       <c r="T13">
-        <v>1.10586506659022</v>
+        <v>1.1184317150742</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>43.175291684238</v>
+        <v>39.57735071055151</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2607,22 +2607,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09683389045851253</v>
+        <v>0.09687889045851254</v>
       </c>
       <c r="C14">
-        <v>99.24033041758526</v>
+        <v>98.08611253656956</v>
       </c>
       <c r="D14">
-        <v>98.33233041758525</v>
+        <v>98.29411253656956</v>
       </c>
       <c r="E14">
-        <v>2.391999999999999</v>
+        <v>3.507999999999999</v>
       </c>
       <c r="F14">
-        <v>13.392</v>
+        <v>14.508</v>
       </c>
       <c r="G14">
         <v>14.3</v>
@@ -2643,28 +2643,28 @@
         <v>26.66</v>
       </c>
       <c r="M14">
-        <v>0.6736175999999999</v>
+        <v>0.7297524</v>
       </c>
       <c r="N14">
-        <v>25.9863824</v>
+        <v>25.9302476</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>25.9863824</v>
+        <v>25.9302476</v>
       </c>
       <c r="Q14">
-        <v>26.8263824</v>
+        <v>26.7702476</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1031794209755824</v>
+        <v>0.1038389545500144</v>
       </c>
       <c r="T14">
-        <v>1.1184317150742</v>
+        <v>1.131287252029076</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>39.57735071055151</v>
+        <v>36.53293911743216</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2689,22 +2689,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09687889045851254</v>
+        <v>0.09692389045851253</v>
       </c>
       <c r="C15">
-        <v>98.08611253656956</v>
+        <v>96.93192435156462</v>
       </c>
       <c r="D15">
-        <v>98.29411253656956</v>
+        <v>98.25592435156462</v>
       </c>
       <c r="E15">
-        <v>3.507999999999999</v>
+        <v>4.624000000000001</v>
       </c>
       <c r="F15">
-        <v>14.508</v>
+        <v>15.624</v>
       </c>
       <c r="G15">
         <v>14.3</v>
@@ -2725,28 +2725,28 @@
         <v>26.66</v>
       </c>
       <c r="M15">
-        <v>0.7297524</v>
+        <v>0.7858872</v>
       </c>
       <c r="N15">
-        <v>25.9302476</v>
+        <v>25.8741128</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>25.9302476</v>
+        <v>25.8741128</v>
       </c>
       <c r="Q15">
-        <v>26.7702476</v>
+        <v>26.7141128</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1038389545500144</v>
+        <v>0.1045138261145495</v>
       </c>
       <c r="T15">
-        <v>1.131287252029076</v>
+        <v>1.144441754959646</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>36.53293911743216</v>
+        <v>33.923443466187</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2771,22 +2771,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09692389045851253</v>
+        <v>0.09696889045851252</v>
       </c>
       <c r="C16">
-        <v>96.93192435156462</v>
+        <v>95.77776582797233</v>
       </c>
       <c r="D16">
-        <v>98.25592435156462</v>
+        <v>98.21776582797234</v>
       </c>
       <c r="E16">
-        <v>4.624000000000001</v>
+        <v>5.740000000000002</v>
       </c>
       <c r="F16">
-        <v>15.624</v>
+        <v>16.74</v>
       </c>
       <c r="G16">
         <v>14.3</v>
@@ -2807,28 +2807,28 @@
         <v>26.66</v>
       </c>
       <c r="M16">
-        <v>0.7858872</v>
+        <v>0.842022</v>
       </c>
       <c r="N16">
-        <v>25.8741128</v>
+        <v>25.817978</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>25.8741128</v>
+        <v>25.817978</v>
       </c>
       <c r="Q16">
-        <v>26.7141128</v>
+        <v>26.657978</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1045138261145495</v>
+        <v>0.1052045770100147</v>
       </c>
       <c r="T16">
-        <v>1.144441754959646</v>
+        <v>1.157905775606231</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>33.923443466187</v>
+        <v>31.6618805684412</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2853,22 +2853,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09696889045851252</v>
+        <v>0.09701389045851253</v>
       </c>
       <c r="C17">
-        <v>95.77776582797235</v>
+        <v>94.62363693124831</v>
       </c>
       <c r="D17">
-        <v>98.21776582797234</v>
+        <v>98.17963693124831</v>
       </c>
       <c r="E17">
-        <v>5.739999999999998</v>
+        <v>6.855999999999998</v>
       </c>
       <c r="F17">
-        <v>16.74</v>
+        <v>17.856</v>
       </c>
       <c r="G17">
         <v>14.3</v>
@@ -2889,28 +2889,28 @@
         <v>26.66</v>
       </c>
       <c r="M17">
-        <v>0.8420219999999998</v>
+        <v>0.8981567999999999</v>
       </c>
       <c r="N17">
-        <v>25.817978</v>
+        <v>25.7618432</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>25.817978</v>
+        <v>25.7618432</v>
       </c>
       <c r="Q17">
-        <v>26.657978</v>
+        <v>26.6018432</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1052045770100147</v>
+        <v>0.1059117743553721</v>
       </c>
       <c r="T17">
-        <v>1.157905775606231</v>
+        <v>1.171690368172971</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>31.66188056844121</v>
+        <v>29.68301303291364</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2935,22 +2935,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09701389045851253</v>
+        <v>0.09705889045851253</v>
       </c>
       <c r="C18">
-        <v>94.62363693124831</v>
+        <v>93.4695376269018</v>
       </c>
       <c r="D18">
-        <v>98.17963693124831</v>
+        <v>98.14153762690181</v>
       </c>
       <c r="E18">
-        <v>6.855999999999998</v>
+        <v>7.972000000000001</v>
       </c>
       <c r="F18">
-        <v>17.856</v>
+        <v>18.972</v>
       </c>
       <c r="G18">
         <v>14.3</v>
@@ -2971,28 +2971,28 @@
         <v>26.66</v>
       </c>
       <c r="M18">
-        <v>0.8981567999999999</v>
+        <v>0.9542916</v>
       </c>
       <c r="N18">
-        <v>25.7618432</v>
+        <v>25.7057084</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>25.7618432</v>
+        <v>25.7057084</v>
       </c>
       <c r="Q18">
-        <v>26.6018432</v>
+        <v>26.5457084</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1059117743553721</v>
+        <v>0.1066360126006175</v>
       </c>
       <c r="T18">
-        <v>1.171690368172971</v>
+        <v>1.185807119596742</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>29.68301303291364</v>
+        <v>27.93695344274224</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09705889045851253</v>
+        <v>0.09710389045851253</v>
       </c>
       <c r="C19">
-        <v>93.4695376269018</v>
+        <v>92.31546788049559</v>
       </c>
       <c r="D19">
-        <v>98.14153762690181</v>
+        <v>98.10346788049559</v>
       </c>
       <c r="E19">
-        <v>7.972000000000001</v>
+        <v>9.088000000000001</v>
       </c>
       <c r="F19">
-        <v>18.972</v>
+        <v>20.088</v>
       </c>
       <c r="G19">
         <v>14.3</v>
@@ -3053,28 +3053,28 @@
         <v>26.66</v>
       </c>
       <c r="M19">
-        <v>0.9542916</v>
+        <v>1.0104264</v>
       </c>
       <c r="N19">
-        <v>25.7057084</v>
+        <v>25.6495736</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>25.7057084</v>
+        <v>25.6495736</v>
       </c>
       <c r="Q19">
-        <v>26.5457084</v>
+        <v>26.4895736</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1066360126006175</v>
+        <v>0.107377915193308</v>
       </c>
       <c r="T19">
-        <v>1.185807119596742</v>
+        <v>1.200268182030849</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>27.93695344274224</v>
+        <v>26.384900473701</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3099,22 +3099,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09710389045851253</v>
+        <v>0.09714889045851252</v>
       </c>
       <c r="C20">
-        <v>92.31546788049559</v>
+        <v>91.16142765764587</v>
       </c>
       <c r="D20">
-        <v>98.10346788049559</v>
+        <v>98.06542765764588</v>
       </c>
       <c r="E20">
-        <v>9.087999999999997</v>
+        <v>10.204</v>
       </c>
       <c r="F20">
-        <v>20.088</v>
+        <v>21.204</v>
       </c>
       <c r="G20">
         <v>14.3</v>
@@ -3135,28 +3135,28 @@
         <v>26.66</v>
       </c>
       <c r="M20">
-        <v>1.0104264</v>
+        <v>1.0665612</v>
       </c>
       <c r="N20">
-        <v>25.6495736</v>
+        <v>25.5934388</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>25.6495736</v>
+        <v>25.5934388</v>
       </c>
       <c r="Q20">
-        <v>26.4895736</v>
+        <v>26.4334388</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.107377915193308</v>
+        <v>0.108138136368534</v>
       </c>
       <c r="T20">
-        <v>1.200268182030849</v>
+        <v>1.215086307734933</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>26.38490047370101</v>
+        <v>24.99622150140095</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3181,22 +3181,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09714889045851252</v>
+        <v>0.09719389045851252</v>
       </c>
       <c r="C21">
-        <v>91.16142765764587</v>
+        <v>90.0074169240221</v>
       </c>
       <c r="D21">
-        <v>98.06542765764588</v>
+        <v>98.02741692402211</v>
       </c>
       <c r="E21">
-        <v>10.204</v>
+        <v>11.32</v>
       </c>
       <c r="F21">
-        <v>21.204</v>
+        <v>22.32</v>
       </c>
       <c r="G21">
         <v>14.3</v>
@@ -3217,28 +3217,28 @@
         <v>26.66</v>
       </c>
       <c r="M21">
-        <v>1.0665612</v>
+        <v>1.122696</v>
       </c>
       <c r="N21">
-        <v>25.5934388</v>
+        <v>25.537304</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>25.5934388</v>
+        <v>25.537304</v>
       </c>
       <c r="Q21">
-        <v>26.4334388</v>
+        <v>26.377304</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.108138136368534</v>
+        <v>0.1089173630731406</v>
       </c>
       <c r="T21">
-        <v>1.215086307734933</v>
+        <v>1.23027488658162</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>24.99622150140095</v>
+        <v>23.7464104263309</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3263,22 +3263,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09719389045851252</v>
+        <v>0.09723889045851253</v>
       </c>
       <c r="C22">
-        <v>90.0074169240221</v>
+        <v>88.85343564534699</v>
       </c>
       <c r="D22">
-        <v>98.02741692402211</v>
+        <v>97.989435645347</v>
       </c>
       <c r="E22">
-        <v>11.32</v>
+        <v>12.436</v>
       </c>
       <c r="F22">
-        <v>22.32</v>
+        <v>23.436</v>
       </c>
       <c r="G22">
         <v>14.3</v>
@@ -3299,28 +3299,28 @@
         <v>26.66</v>
       </c>
       <c r="M22">
-        <v>1.122696</v>
+        <v>1.1788308</v>
       </c>
       <c r="N22">
-        <v>25.537304</v>
+        <v>25.4811692</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>25.537304</v>
+        <v>25.4811692</v>
       </c>
       <c r="Q22">
-        <v>26.377304</v>
+        <v>26.3211692</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1089173630731406</v>
+        <v>0.1097163170360918</v>
       </c>
       <c r="T22">
-        <v>1.23027488658162</v>
+        <v>1.245847986411767</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>23.7464104263309</v>
+        <v>22.61562897745801</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3345,22 +3345,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09723889045851253</v>
+        <v>0.09728389045851252</v>
       </c>
       <c r="C23">
-        <v>88.85343564534701</v>
+        <v>87.69948378739636</v>
       </c>
       <c r="D23">
-        <v>97.989435645347</v>
+        <v>97.95148378739637</v>
       </c>
       <c r="E23">
-        <v>12.436</v>
+        <v>13.552</v>
       </c>
       <c r="F23">
-        <v>23.436</v>
+        <v>24.552</v>
       </c>
       <c r="G23">
         <v>14.3</v>
@@ -3381,28 +3381,28 @@
         <v>26.66</v>
       </c>
       <c r="M23">
-        <v>1.1788308</v>
+        <v>1.2349656</v>
       </c>
       <c r="N23">
-        <v>25.4811692</v>
+        <v>25.4250344</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>25.4811692</v>
+        <v>25.4250344</v>
       </c>
       <c r="Q23">
-        <v>26.3211692</v>
+        <v>26.2650344</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1097163170360918</v>
+        <v>0.110535756998093</v>
       </c>
       <c r="T23">
-        <v>1.245847986411767</v>
+        <v>1.261820396493969</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>22.61562897745801</v>
+        <v>21.58764584211901</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3427,22 +3427,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09728389045851252</v>
+        <v>0.09732889045851252</v>
       </c>
       <c r="C24">
-        <v>87.69948378739636</v>
+        <v>86.54556131599898</v>
       </c>
       <c r="D24">
-        <v>97.95148378739637</v>
+        <v>97.91356131599898</v>
       </c>
       <c r="E24">
-        <v>13.552</v>
+        <v>14.668</v>
       </c>
       <c r="F24">
-        <v>24.552</v>
+        <v>25.668</v>
       </c>
       <c r="G24">
         <v>14.3</v>
@@ -3463,28 +3463,28 @@
         <v>26.66</v>
       </c>
       <c r="M24">
-        <v>1.2349656</v>
+        <v>1.2911004</v>
       </c>
       <c r="N24">
-        <v>25.4250344</v>
+        <v>25.3688996</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>25.4250344</v>
+        <v>25.3688996</v>
       </c>
       <c r="Q24">
-        <v>26.2650344</v>
+        <v>26.2088996</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.110535756998093</v>
+        <v>0.1113764811149513</v>
       </c>
       <c r="T24">
-        <v>1.261820396493969</v>
+        <v>1.278207674370514</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>21.58764584211901</v>
+        <v>20.64905254463557</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3509,22 +3509,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09732889045851252</v>
+        <v>0.09737389045851252</v>
       </c>
       <c r="C25">
-        <v>86.54556131599898</v>
+        <v>85.39166819703654</v>
       </c>
       <c r="D25">
-        <v>97.91356131599898</v>
+        <v>97.87566819703655</v>
       </c>
       <c r="E25">
-        <v>14.668</v>
+        <v>15.784</v>
       </c>
       <c r="F25">
-        <v>25.668</v>
+        <v>26.784</v>
       </c>
       <c r="G25">
         <v>14.3</v>
@@ -3545,28 +3545,28 @@
         <v>26.66</v>
       </c>
       <c r="M25">
-        <v>1.2911004</v>
+        <v>1.3472352</v>
       </c>
       <c r="N25">
-        <v>25.3688996</v>
+        <v>25.3127648</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>25.3688996</v>
+        <v>25.3127648</v>
       </c>
       <c r="Q25">
-        <v>26.2088996</v>
+        <v>26.1527648</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1113764811149513</v>
+        <v>0.1122393295506744</v>
       </c>
       <c r="T25">
-        <v>1.278207674370514</v>
+        <v>1.295026196401705</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>20.64905254463557</v>
+        <v>19.78867535527575</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3591,22 +3591,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09737389045851252</v>
+        <v>0.09741889045851254</v>
       </c>
       <c r="C26">
-        <v>85.39166819703655</v>
+        <v>84.23780439644355</v>
       </c>
       <c r="D26">
-        <v>97.87566819703655</v>
+        <v>97.83780439644354</v>
       </c>
       <c r="E26">
-        <v>15.784</v>
+        <v>16.9</v>
       </c>
       <c r="F26">
-        <v>26.784</v>
+        <v>27.9</v>
       </c>
       <c r="G26">
         <v>14.3</v>
@@ -3627,28 +3627,28 @@
         <v>26.66</v>
       </c>
       <c r="M26">
-        <v>1.3472352</v>
+        <v>1.40337</v>
       </c>
       <c r="N26">
-        <v>25.3127648</v>
+        <v>25.25663</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>25.3127648</v>
+        <v>25.25663</v>
       </c>
       <c r="Q26">
-        <v>26.1527648</v>
+        <v>26.09663</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1122393295506744</v>
+        <v>0.1131251872780167</v>
       </c>
       <c r="T26">
-        <v>1.295026196401705</v>
+        <v>1.312293212353728</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>19.78867535527575</v>
+        <v>18.99712834106473</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3673,22 +3673,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09741889045851254</v>
+        <v>0.0974638904585125</v>
       </c>
       <c r="C27">
-        <v>84.23780439644355</v>
+        <v>83.08396988020723</v>
       </c>
       <c r="D27">
-        <v>97.83780439644354</v>
+        <v>97.79996988020724</v>
       </c>
       <c r="E27">
-        <v>16.9</v>
+        <v>18.016</v>
       </c>
       <c r="F27">
-        <v>27.9</v>
+        <v>29.016</v>
       </c>
       <c r="G27">
         <v>14.3</v>
@@ -3709,28 +3709,28 @@
         <v>26.66</v>
       </c>
       <c r="M27">
-        <v>1.40337</v>
+        <v>1.4595048</v>
       </c>
       <c r="N27">
-        <v>25.25663</v>
+        <v>25.2004952</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>25.25663</v>
+        <v>25.2004952</v>
       </c>
       <c r="Q27">
-        <v>26.09663</v>
+        <v>26.0404952</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1131251872780167</v>
+        <v>0.114034987106098</v>
       </c>
       <c r="T27">
-        <v>1.312293212353728</v>
+        <v>1.330026904412562</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>18.99712834106473</v>
+        <v>18.26646955871608</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3755,22 +3755,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0974638904585125</v>
+        <v>0.09750889045851252</v>
       </c>
       <c r="C28">
-        <v>83.08396988020723</v>
+        <v>81.9301646143673</v>
       </c>
       <c r="D28">
-        <v>97.79996988020724</v>
+        <v>97.76216461436731</v>
       </c>
       <c r="E28">
-        <v>18.016</v>
+        <v>19.132</v>
       </c>
       <c r="F28">
-        <v>29.016</v>
+        <v>30.132</v>
       </c>
       <c r="G28">
         <v>14.3</v>
@@ -3791,28 +3791,28 @@
         <v>26.66</v>
       </c>
       <c r="M28">
-        <v>1.4595048</v>
+        <v>1.5156396</v>
       </c>
       <c r="N28">
-        <v>25.2004952</v>
+        <v>25.1443604</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>25.2004952</v>
+        <v>25.1443604</v>
       </c>
       <c r="Q28">
-        <v>26.0404952</v>
+        <v>25.9843604</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.114034987106098</v>
+        <v>0.1149697129568665</v>
       </c>
       <c r="T28">
-        <v>1.330026904412562</v>
+        <v>1.348246451048351</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>18.26646955871608</v>
+        <v>17.589933649134</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3837,22 +3837,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09750889045851252</v>
+        <v>0.09755389045851252</v>
       </c>
       <c r="C29">
-        <v>81.9301646143673</v>
+        <v>80.77638856501605</v>
       </c>
       <c r="D29">
-        <v>97.76216461436731</v>
+        <v>97.72438856501606</v>
       </c>
       <c r="E29">
-        <v>19.132</v>
+        <v>20.248</v>
       </c>
       <c r="F29">
-        <v>30.132</v>
+        <v>31.248</v>
       </c>
       <c r="G29">
         <v>14.3</v>
@@ -3873,28 +3873,28 @@
         <v>26.66</v>
       </c>
       <c r="M29">
-        <v>1.5156396</v>
+        <v>1.5717744</v>
       </c>
       <c r="N29">
-        <v>25.1443604</v>
+        <v>25.0882256</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>25.1443604</v>
+        <v>25.0882256</v>
       </c>
       <c r="Q29">
-        <v>25.9843604</v>
+        <v>25.9282256</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1149697129568665</v>
+        <v>0.1159304034146007</v>
       </c>
       <c r="T29">
-        <v>1.348246451048351</v>
+        <v>1.3669720962018</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>17.589933649134</v>
+        <v>16.9617217330935</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3919,22 +3919,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09755389045851252</v>
+        <v>0.09759889045851254</v>
       </c>
       <c r="C30">
-        <v>80.77638856501605</v>
+        <v>79.62264169829814</v>
       </c>
       <c r="D30">
-        <v>97.72438856501606</v>
+        <v>97.68664169829815</v>
       </c>
       <c r="E30">
-        <v>20.248</v>
+        <v>21.364</v>
       </c>
       <c r="F30">
-        <v>31.248</v>
+        <v>32.364</v>
       </c>
       <c r="G30">
         <v>14.3</v>
@@ -3955,28 +3955,28 @@
         <v>26.66</v>
       </c>
       <c r="M30">
-        <v>1.5717744</v>
+        <v>1.6279092</v>
       </c>
       <c r="N30">
-        <v>25.0882256</v>
+        <v>25.0320908</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>25.0882256</v>
+        <v>25.0320908</v>
       </c>
       <c r="Q30">
-        <v>25.9282256</v>
+        <v>25.8720908</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1159304034146007</v>
+        <v>0.1169181555753698</v>
       </c>
       <c r="T30">
-        <v>1.3669720962018</v>
+        <v>1.386225224317318</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>16.9617217330935</v>
+        <v>16.37683477677993</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4001,22 +4001,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09759889045851251</v>
+        <v>0.09764389045851252</v>
       </c>
       <c r="C31">
-        <v>79.62264169829817</v>
+        <v>78.46892398041055</v>
       </c>
       <c r="D31">
-        <v>97.68664169829817</v>
+        <v>97.64892398041056</v>
       </c>
       <c r="E31">
-        <v>21.364</v>
+        <v>22.48</v>
       </c>
       <c r="F31">
-        <v>32.364</v>
+        <v>33.48</v>
       </c>
       <c r="G31">
         <v>14.3</v>
@@ -4037,28 +4037,28 @@
         <v>26.66</v>
       </c>
       <c r="M31">
-        <v>1.6279092</v>
+        <v>1.684044</v>
       </c>
       <c r="N31">
-        <v>25.0320908</v>
+        <v>24.975956</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>25.0320908</v>
+        <v>24.975956</v>
       </c>
       <c r="Q31">
-        <v>25.8720908</v>
+        <v>25.815956</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1169181555753697</v>
+        <v>0.1179341292264465</v>
       </c>
       <c r="T31">
-        <v>1.386225224317318</v>
+        <v>1.406028441807566</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>16.37683477677994</v>
+        <v>15.83094028422061</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09764389045851252</v>
+        <v>0.09768889045851252</v>
       </c>
       <c r="C32">
-        <v>78.46892398041055</v>
+        <v>77.31523537760236</v>
       </c>
       <c r="D32">
-        <v>97.64892398041056</v>
+        <v>97.61123537760236</v>
       </c>
       <c r="E32">
-        <v>22.48</v>
+        <v>23.596</v>
       </c>
       <c r="F32">
-        <v>33.48</v>
+        <v>34.596</v>
       </c>
       <c r="G32">
         <v>14.3</v>
@@ -4119,28 +4119,28 @@
         <v>26.66</v>
       </c>
       <c r="M32">
-        <v>1.684044</v>
+        <v>1.7401788</v>
       </c>
       <c r="N32">
-        <v>24.975956</v>
+        <v>24.9198212</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>24.975956</v>
+        <v>24.9198212</v>
       </c>
       <c r="Q32">
-        <v>25.815956</v>
+        <v>25.7598212</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1179341292264465</v>
+        <v>0.1189795513891486</v>
       </c>
       <c r="T32">
-        <v>1.406028441807566</v>
+        <v>1.426405665601878</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>15.83094028422061</v>
+        <v>15.32026479118123</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4165,22 +4165,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09768889045851252</v>
+        <v>0.09773389045851252</v>
       </c>
       <c r="C33">
-        <v>77.31523537760236</v>
+        <v>76.16157585617481</v>
       </c>
       <c r="D33">
-        <v>97.61123537760236</v>
+        <v>97.5735758561748</v>
       </c>
       <c r="E33">
-        <v>23.596</v>
+        <v>24.712</v>
       </c>
       <c r="F33">
-        <v>34.596</v>
+        <v>35.712</v>
       </c>
       <c r="G33">
         <v>14.3</v>
@@ -4201,28 +4201,28 @@
         <v>26.66</v>
       </c>
       <c r="M33">
-        <v>1.7401788</v>
+        <v>1.7963136</v>
       </c>
       <c r="N33">
-        <v>24.9198212</v>
+        <v>24.8636864</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>24.9198212</v>
+        <v>24.8636864</v>
       </c>
       <c r="Q33">
-        <v>25.7598212</v>
+        <v>25.7036864</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1189795513891486</v>
+        <v>0.1200557212625184</v>
       </c>
       <c r="T33">
-        <v>1.426405665601878</v>
+        <v>1.447382219507788</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>15.32026479118123</v>
+        <v>14.84150651645682</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4247,22 +4247,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09773389045851252</v>
+        <v>0.09777889045851253</v>
       </c>
       <c r="C34">
-        <v>76.16157585617481</v>
+        <v>75.00794538248105</v>
       </c>
       <c r="D34">
-        <v>97.5735758561748</v>
+        <v>97.53594538248106</v>
       </c>
       <c r="E34">
-        <v>24.712</v>
+        <v>25.828</v>
       </c>
       <c r="F34">
-        <v>35.712</v>
+        <v>36.828</v>
       </c>
       <c r="G34">
         <v>14.3</v>
@@ -4283,28 +4283,28 @@
         <v>26.66</v>
       </c>
       <c r="M34">
-        <v>1.7963136</v>
+        <v>1.8524484</v>
       </c>
       <c r="N34">
-        <v>24.8636864</v>
+        <v>24.8075516</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>24.8636864</v>
+        <v>24.8075516</v>
       </c>
       <c r="Q34">
-        <v>25.7036864</v>
+        <v>25.6475516</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1200557212625184</v>
+        <v>0.1211640156097202</v>
       </c>
       <c r="T34">
-        <v>1.447382219507788</v>
+        <v>1.468984939201934</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>14.84150651645682</v>
+        <v>14.391763894746</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4329,22 +4329,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09777889045851253</v>
+        <v>0.09782389045851253</v>
       </c>
       <c r="C35">
-        <v>75.00794538248105</v>
+        <v>73.85434392292625</v>
       </c>
       <c r="D35">
-        <v>97.53594538248106</v>
+        <v>97.49834392292625</v>
       </c>
       <c r="E35">
-        <v>25.828</v>
+        <v>26.944</v>
       </c>
       <c r="F35">
-        <v>36.828</v>
+        <v>37.944</v>
       </c>
       <c r="G35">
         <v>14.3</v>
@@ -4365,28 +4365,28 @@
         <v>26.66</v>
       </c>
       <c r="M35">
-        <v>1.8524484</v>
+        <v>1.9085832</v>
       </c>
       <c r="N35">
-        <v>24.8075516</v>
+        <v>24.7514168</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>24.8075516</v>
+        <v>24.7514168</v>
       </c>
       <c r="Q35">
-        <v>25.6475516</v>
+        <v>25.5914168</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1211640156097202</v>
+        <v>0.1223058946341099</v>
       </c>
       <c r="T35">
-        <v>1.468984939201934</v>
+        <v>1.4912422867656</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>14.391763894746</v>
+        <v>13.96847672137112</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4411,22 +4411,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09782389045851253</v>
+        <v>0.09786889045851252</v>
       </c>
       <c r="C36">
-        <v>73.85434392292625</v>
+        <v>72.70077144396724</v>
       </c>
       <c r="D36">
-        <v>97.49834392292625</v>
+        <v>97.46077144396725</v>
       </c>
       <c r="E36">
-        <v>26.944</v>
+        <v>28.06</v>
       </c>
       <c r="F36">
-        <v>37.944</v>
+        <v>39.06</v>
       </c>
       <c r="G36">
         <v>14.3</v>
@@ -4447,28 +4447,28 @@
         <v>26.66</v>
       </c>
       <c r="M36">
-        <v>1.9085832</v>
+        <v>1.964718</v>
       </c>
       <c r="N36">
-        <v>24.7514168</v>
+        <v>24.695282</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>24.7514168</v>
+        <v>24.695282</v>
       </c>
       <c r="Q36">
-        <v>25.5914168</v>
+        <v>25.535282</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1223058946341099</v>
+        <v>0.1234829083977116</v>
       </c>
       <c r="T36">
-        <v>1.4912422867656</v>
+        <v>1.514184475792763</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>13.96847672137112</v>
+        <v>13.5693773864748</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4493,22 +4493,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09786889045851252</v>
+        <v>0.09791389045851251</v>
       </c>
       <c r="C37">
-        <v>72.70077144396724</v>
+        <v>71.5472279121126</v>
       </c>
       <c r="D37">
-        <v>97.46077144396725</v>
+        <v>97.42322791211261</v>
       </c>
       <c r="E37">
-        <v>28.06</v>
+        <v>29.176</v>
       </c>
       <c r="F37">
-        <v>39.06</v>
+        <v>40.176</v>
       </c>
       <c r="G37">
         <v>14.3</v>
@@ -4529,28 +4529,28 @@
         <v>26.66</v>
       </c>
       <c r="M37">
-        <v>1.964718</v>
+        <v>2.0208528</v>
       </c>
       <c r="N37">
-        <v>24.695282</v>
+        <v>24.6391472</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>24.695282</v>
+        <v>24.6391472</v>
       </c>
       <c r="Q37">
-        <v>25.535282</v>
+        <v>25.4791472</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1234829083977116</v>
+        <v>0.1246967038414258</v>
       </c>
       <c r="T37">
-        <v>1.514184475792763</v>
+        <v>1.537843608227025</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>13.5693773864748</v>
+        <v>13.1924502368505</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4575,22 +4575,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09791389045851252</v>
+        <v>0.09851389045851253</v>
       </c>
       <c r="C38">
-        <v>71.54722791211259</v>
+        <v>69.9333972893578</v>
       </c>
       <c r="D38">
-        <v>97.42322791211259</v>
+        <v>96.9253972893578</v>
       </c>
       <c r="E38">
-        <v>29.17599999999999</v>
+        <v>30.29199999999999</v>
       </c>
       <c r="F38">
-        <v>40.17599999999999</v>
+        <v>41.29199999999999</v>
       </c>
       <c r="G38">
         <v>14.3</v>
@@ -4611,45 +4611,45 @@
         <v>26.66</v>
       </c>
       <c r="M38">
-        <v>2.0208528</v>
+        <v>2.1389256</v>
       </c>
       <c r="N38">
-        <v>24.6391472</v>
+        <v>24.5210744</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>24.6391472</v>
+        <v>24.5210744</v>
       </c>
       <c r="Q38">
-        <v>25.4791472</v>
+        <v>25.3610744</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1246967038414258</v>
+        <v>0.1259490324738294</v>
       </c>
       <c r="T38">
-        <v>1.537843608227025</v>
+        <v>1.562253824230629</v>
       </c>
       <c r="U38">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V38">
         <v>0</v>
       </c>
       <c r="W38">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y38">
-        <v>13.1924502368505</v>
+        <v>12.46420165339084</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4657,22 +4657,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09851389045851253</v>
+        <v>0.0985738904585125</v>
       </c>
       <c r="C39">
-        <v>69.9333972893578</v>
+        <v>68.76789391359158</v>
       </c>
       <c r="D39">
-        <v>96.9253972893578</v>
+        <v>96.87589391359158</v>
       </c>
       <c r="E39">
-        <v>30.29199999999999</v>
+        <v>31.408</v>
       </c>
       <c r="F39">
-        <v>41.29199999999999</v>
+        <v>42.408</v>
       </c>
       <c r="G39">
         <v>14.3</v>
@@ -4693,28 +4693,28 @@
         <v>26.66</v>
       </c>
       <c r="M39">
-        <v>2.1389256</v>
+        <v>2.1967344</v>
       </c>
       <c r="N39">
-        <v>24.5210744</v>
+        <v>24.4632656</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>24.5210744</v>
+        <v>24.4632656</v>
       </c>
       <c r="Q39">
-        <v>25.3610744</v>
+        <v>25.3032656</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1259490324738294</v>
+        <v>0.1272417588040524</v>
       </c>
       <c r="T39">
-        <v>1.562253824230629</v>
+        <v>1.587451466556929</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>12.46420165339084</v>
+        <v>12.13619634672266</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4739,22 +4739,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0985738904585125</v>
+        <v>0.09863389045851252</v>
       </c>
       <c r="C40">
-        <v>68.76789391359158</v>
+        <v>67.60244107841254</v>
       </c>
       <c r="D40">
-        <v>96.87589391359158</v>
+        <v>96.82644107841254</v>
       </c>
       <c r="E40">
-        <v>31.408</v>
+        <v>32.524</v>
       </c>
       <c r="F40">
-        <v>42.408</v>
+        <v>43.524</v>
       </c>
       <c r="G40">
         <v>14.3</v>
@@ -4775,28 +4775,28 @@
         <v>26.66</v>
       </c>
       <c r="M40">
-        <v>2.1967344</v>
+        <v>2.2545432</v>
       </c>
       <c r="N40">
-        <v>24.4632656</v>
+        <v>24.4054568</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>24.4632656</v>
+        <v>24.4054568</v>
       </c>
       <c r="Q40">
-        <v>25.3032656</v>
+        <v>25.2454568</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1272417588040524</v>
+        <v>0.1285768696041189</v>
       </c>
       <c r="T40">
-        <v>1.587451466556929</v>
+        <v>1.613475261090649</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>12.13619634672266</v>
+        <v>11.82501182501182</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4821,22 +4821,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09863389045851252</v>
+        <v>0.09869389045851251</v>
       </c>
       <c r="C41">
-        <v>67.60244107841254</v>
+        <v>66.43703870646094</v>
       </c>
       <c r="D41">
-        <v>96.82644107841254</v>
+        <v>96.77703870646094</v>
       </c>
       <c r="E41">
-        <v>32.524</v>
+        <v>33.64</v>
       </c>
       <c r="F41">
-        <v>43.524</v>
+        <v>44.64</v>
       </c>
       <c r="G41">
         <v>14.3</v>
@@ -4857,28 +4857,28 @@
         <v>26.66</v>
       </c>
       <c r="M41">
-        <v>2.2545432</v>
+        <v>2.312352</v>
       </c>
       <c r="N41">
-        <v>24.4054568</v>
+        <v>24.347648</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>24.4054568</v>
+        <v>24.347648</v>
       </c>
       <c r="Q41">
-        <v>25.2454568</v>
+        <v>25.187648</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1285768696041189</v>
+        <v>0.1299564840975209</v>
       </c>
       <c r="T41">
-        <v>1.613475261090649</v>
+        <v>1.64036651544216</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>11.82501182501182</v>
+        <v>11.52938652938653</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4903,22 +4903,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09869389045851251</v>
+        <v>0.09875389045851252</v>
       </c>
       <c r="C42">
-        <v>66.43703870646094</v>
+        <v>65.27168672053472</v>
       </c>
       <c r="D42">
-        <v>96.77703870646094</v>
+        <v>96.72768672053472</v>
       </c>
       <c r="E42">
-        <v>33.64</v>
+        <v>34.756</v>
       </c>
       <c r="F42">
-        <v>44.64</v>
+        <v>45.756</v>
       </c>
       <c r="G42">
         <v>14.3</v>
@@ -4939,28 +4939,28 @@
         <v>26.66</v>
       </c>
       <c r="M42">
-        <v>2.312352</v>
+        <v>2.3701608</v>
       </c>
       <c r="N42">
-        <v>24.347648</v>
+        <v>24.2898392</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>24.347648</v>
+        <v>24.2898392</v>
       </c>
       <c r="Q42">
-        <v>25.187648</v>
+        <v>25.1298392</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1299564840975209</v>
+        <v>0.1313828651839195</v>
       </c>
       <c r="T42">
-        <v>1.64036651544216</v>
+        <v>1.66816933773779</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4977,7 +4977,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>11.52938652938653</v>
+        <v>11.2481819798893</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4985,22 +4985,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09875389045851252</v>
+        <v>0.09881389045851252</v>
       </c>
       <c r="C43">
-        <v>65.27168672053472</v>
+        <v>64.1063850435893</v>
       </c>
       <c r="D43">
-        <v>96.72768672053472</v>
+        <v>96.6783850435893</v>
       </c>
       <c r="E43">
-        <v>34.756</v>
+        <v>35.872</v>
       </c>
       <c r="F43">
-        <v>45.756</v>
+        <v>46.872</v>
       </c>
       <c r="G43">
         <v>14.3</v>
@@ -5021,28 +5021,28 @@
         <v>26.66</v>
       </c>
       <c r="M43">
-        <v>2.3701608</v>
+        <v>2.4279696</v>
       </c>
       <c r="N43">
-        <v>24.2898392</v>
+        <v>24.2320304</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>24.2898392</v>
+        <v>24.2320304</v>
       </c>
       <c r="Q43">
-        <v>25.1298392</v>
+        <v>25.0720304</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1313828651839195</v>
+        <v>0.1328584318250216</v>
       </c>
       <c r="T43">
-        <v>1.66816933773779</v>
+        <v>1.696930878043614</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -5059,7 +5059,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>11.2481819798893</v>
+        <v>10.98036812322527</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5067,22 +5067,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09881389045851252</v>
+        <v>0.09887389045851254</v>
       </c>
       <c r="C44">
-        <v>64.10638504358931</v>
+        <v>62.94113359873704</v>
       </c>
       <c r="D44">
-        <v>96.6783850435893</v>
+        <v>96.62913359873704</v>
       </c>
       <c r="E44">
-        <v>35.87199999999999</v>
+        <v>36.988</v>
       </c>
       <c r="F44">
-        <v>46.87199999999999</v>
+        <v>47.988</v>
       </c>
       <c r="G44">
         <v>14.3</v>
@@ -5103,28 +5103,28 @@
         <v>26.66</v>
       </c>
       <c r="M44">
-        <v>2.4279696</v>
+        <v>2.4857784</v>
       </c>
       <c r="N44">
-        <v>24.2320304</v>
+        <v>24.1742216</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>24.2320304</v>
+        <v>24.1742216</v>
       </c>
       <c r="Q44">
-        <v>25.0720304</v>
+        <v>25.0142216</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1328584318250216</v>
+        <v>0.1343857727342325</v>
       </c>
       <c r="T44">
-        <v>1.696930878043613</v>
+        <v>1.726701595202274</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>10.98036812322527</v>
+        <v>10.72501072501072</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09887389045851254</v>
+        <v>0.09893389045851253</v>
       </c>
       <c r="C45">
-        <v>62.94113359873704</v>
+        <v>61.77593230924698</v>
       </c>
       <c r="D45">
-        <v>96.62913359873704</v>
+        <v>96.57993230924698</v>
       </c>
       <c r="E45">
-        <v>36.988</v>
+        <v>38.104</v>
       </c>
       <c r="F45">
-        <v>47.988</v>
+        <v>49.104</v>
       </c>
       <c r="G45">
         <v>14.3</v>
@@ -5185,28 +5185,28 @@
         <v>26.66</v>
       </c>
       <c r="M45">
-        <v>2.4857784</v>
+        <v>2.5435872</v>
       </c>
       <c r="N45">
-        <v>24.1742216</v>
+        <v>24.1164128</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>24.1742216</v>
+        <v>24.1164128</v>
       </c>
       <c r="Q45">
-        <v>25.0142216</v>
+        <v>24.9564128</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1343857727342325</v>
+        <v>0.1359676615330581</v>
       </c>
       <c r="T45">
-        <v>1.726701595202274</v>
+        <v>1.757535552259457</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>10.72501072501072</v>
+        <v>10.48126048126048</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5231,22 +5231,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09893389045851253</v>
+        <v>0.09899389045851252</v>
       </c>
       <c r="C46">
-        <v>61.77593230924698</v>
+        <v>60.61078109854429</v>
       </c>
       <c r="D46">
-        <v>96.57993230924698</v>
+        <v>96.5307810985443</v>
       </c>
       <c r="E46">
-        <v>38.104</v>
+        <v>39.22</v>
       </c>
       <c r="F46">
-        <v>49.104</v>
+        <v>50.22</v>
       </c>
       <c r="G46">
         <v>14.3</v>
@@ -5267,28 +5267,28 @@
         <v>26.66</v>
       </c>
       <c r="M46">
-        <v>2.5435872</v>
+        <v>2.601396</v>
       </c>
       <c r="N46">
-        <v>24.1164128</v>
+        <v>24.058604</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>24.1164128</v>
+        <v>24.058604</v>
       </c>
       <c r="Q46">
-        <v>24.9564128</v>
+        <v>24.898604</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1359676615330581</v>
+        <v>0.1376070735609319</v>
       </c>
       <c r="T46">
-        <v>1.757535552259457</v>
+        <v>1.78949074411872</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>10.48126048126048</v>
+        <v>10.24834358167691</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5313,22 +5313,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09899389045851252</v>
+        <v>0.09905389045851254</v>
       </c>
       <c r="C47">
-        <v>60.61078109854429</v>
+        <v>59.44567989020992</v>
       </c>
       <c r="D47">
-        <v>96.5307810985443</v>
+        <v>96.48167989020992</v>
       </c>
       <c r="E47">
-        <v>39.22</v>
+        <v>40.336</v>
       </c>
       <c r="F47">
-        <v>50.22</v>
+        <v>51.336</v>
       </c>
       <c r="G47">
         <v>14.3</v>
@@ -5349,28 +5349,28 @@
         <v>26.66</v>
       </c>
       <c r="M47">
-        <v>2.601396</v>
+        <v>2.6592048</v>
       </c>
       <c r="N47">
-        <v>24.058604</v>
+        <v>24.0007952</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>24.058604</v>
+        <v>24.0007952</v>
       </c>
       <c r="Q47">
-        <v>24.898604</v>
+        <v>24.8407952</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1376070735609319</v>
+        <v>0.139307204552801</v>
       </c>
       <c r="T47">
-        <v>1.78949074411872</v>
+        <v>1.8226294616024</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5387,7 +5387,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>10.24834358167691</v>
+        <v>10.02555350381437</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5395,22 +5395,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09905389045851254</v>
+        <v>0.09911389045851254</v>
       </c>
       <c r="C48">
-        <v>59.44567989020992</v>
+        <v>58.28062860798029</v>
       </c>
       <c r="D48">
-        <v>96.48167989020992</v>
+        <v>96.43262860798029</v>
       </c>
       <c r="E48">
-        <v>40.336</v>
+        <v>41.452</v>
       </c>
       <c r="F48">
-        <v>51.336</v>
+        <v>52.452</v>
       </c>
       <c r="G48">
         <v>14.3</v>
@@ -5431,28 +5431,28 @@
         <v>26.66</v>
       </c>
       <c r="M48">
-        <v>2.6592048</v>
+        <v>2.7170136</v>
       </c>
       <c r="N48">
-        <v>24.0007952</v>
+        <v>23.9429864</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>24.0007952</v>
+        <v>23.9429864</v>
       </c>
       <c r="Q48">
-        <v>24.8407952</v>
+        <v>24.7829864</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.139307204552801</v>
+        <v>0.1410714914311557</v>
       </c>
       <c r="T48">
-        <v>1.8226294616024</v>
+        <v>1.857018696726974</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>10.02555350381437</v>
+        <v>9.812243854797046</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5477,22 +5477,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09911389045851254</v>
+        <v>0.09998989045851253</v>
       </c>
       <c r="C49">
-        <v>58.28062860798029</v>
+        <v>56.45411784262487</v>
       </c>
       <c r="D49">
-        <v>96.43262860798029</v>
+        <v>95.72211784262488</v>
       </c>
       <c r="E49">
-        <v>41.452</v>
+        <v>42.568</v>
       </c>
       <c r="F49">
-        <v>52.452</v>
+        <v>53.568</v>
       </c>
       <c r="G49">
         <v>14.3</v>
@@ -5513,45 +5513,45 @@
         <v>26.66</v>
       </c>
       <c r="M49">
-        <v>2.7170136</v>
+        <v>2.865888</v>
       </c>
       <c r="N49">
-        <v>23.9429864</v>
+        <v>23.794112</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>23.9429864</v>
+        <v>23.794112</v>
       </c>
       <c r="Q49">
-        <v>24.7829864</v>
+        <v>24.634112</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1410714914311557</v>
+        <v>0.1429036354971395</v>
       </c>
       <c r="T49">
-        <v>1.857018696726974</v>
+        <v>1.892730594740954</v>
       </c>
       <c r="U49">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V49">
         <v>0</v>
       </c>
       <c r="W49">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>9.812243854797046</v>
+        <v>9.302526825891311</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5559,22 +5559,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09998989045851252</v>
+        <v>0.1000668904585125</v>
       </c>
       <c r="C50">
-        <v>56.4541178426249</v>
+        <v>55.27616454896088</v>
       </c>
       <c r="D50">
-        <v>95.7221178426249</v>
+        <v>95.66016454896088</v>
       </c>
       <c r="E50">
-        <v>42.568</v>
+        <v>43.684</v>
       </c>
       <c r="F50">
-        <v>53.568</v>
+        <v>54.684</v>
       </c>
       <c r="G50">
         <v>14.3</v>
@@ -5595,28 +5595,28 @@
         <v>26.66</v>
       </c>
       <c r="M50">
-        <v>2.865888</v>
+        <v>2.925594</v>
       </c>
       <c r="N50">
-        <v>23.794112</v>
+        <v>23.734406</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>23.794112</v>
+        <v>23.734406</v>
       </c>
       <c r="Q50">
-        <v>24.634112</v>
+        <v>24.574406</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1429036354971395</v>
+        <v>0.1448076283500246</v>
       </c>
       <c r="T50">
-        <v>1.892730594740953</v>
+        <v>1.929842959343717</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>9.302526825891311</v>
+        <v>9.112679339648633</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5641,22 +5641,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1000668904585125</v>
+        <v>0.1001438904585125</v>
       </c>
       <c r="C51">
-        <v>55.27616454896088</v>
+        <v>54.09829139827995</v>
       </c>
       <c r="D51">
-        <v>95.66016454896088</v>
+        <v>95.59829139827995</v>
       </c>
       <c r="E51">
-        <v>43.684</v>
+        <v>44.8</v>
       </c>
       <c r="F51">
-        <v>54.684</v>
+        <v>55.8</v>
       </c>
       <c r="G51">
         <v>14.3</v>
@@ -5677,28 +5677,28 @@
         <v>26.66</v>
       </c>
       <c r="M51">
-        <v>2.925594</v>
+        <v>2.9853</v>
       </c>
       <c r="N51">
-        <v>23.734406</v>
+        <v>23.6747</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>23.734406</v>
+        <v>23.6747</v>
       </c>
       <c r="Q51">
-        <v>24.574406</v>
+        <v>24.5147</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1448076283500246</v>
+        <v>0.146787780917025</v>
       </c>
       <c r="T51">
-        <v>1.929842959343717</v>
+        <v>1.968439818530592</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>9.112679339648633</v>
+        <v>8.930425752855662</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5723,22 +5723,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1001438904585125</v>
+        <v>0.1002208904585125</v>
       </c>
       <c r="C52">
-        <v>54.09829139827995</v>
+        <v>52.92049823517277</v>
       </c>
       <c r="D52">
-        <v>95.59829139827995</v>
+        <v>95.53649823517277</v>
       </c>
       <c r="E52">
-        <v>44.8</v>
+        <v>45.916</v>
       </c>
       <c r="F52">
-        <v>55.8</v>
+        <v>56.916</v>
       </c>
       <c r="G52">
         <v>14.3</v>
@@ -5759,28 +5759,28 @@
         <v>26.66</v>
       </c>
       <c r="M52">
-        <v>2.9853</v>
+        <v>3.045006</v>
       </c>
       <c r="N52">
-        <v>23.6747</v>
+        <v>23.614994</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>23.6747</v>
+        <v>23.614994</v>
       </c>
       <c r="Q52">
-        <v>24.5147</v>
+        <v>24.454994</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.146787780917025</v>
+        <v>0.1488487560377807</v>
       </c>
       <c r="T52">
-        <v>1.968439818530592</v>
+        <v>2.008612059725094</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>8.930425752855662</v>
+        <v>8.755319365544764</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5805,22 +5805,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1002208904585125</v>
+        <v>0.1002978904585125</v>
       </c>
       <c r="C53">
-        <v>52.92049823517277</v>
+        <v>51.74278490463158</v>
       </c>
       <c r="D53">
-        <v>95.53649823517277</v>
+        <v>95.47478490463158</v>
       </c>
       <c r="E53">
-        <v>45.916</v>
+        <v>47.032</v>
       </c>
       <c r="F53">
-        <v>56.916</v>
+        <v>58.032</v>
       </c>
       <c r="G53">
         <v>14.3</v>
@@ -5841,28 +5841,28 @@
         <v>26.66</v>
       </c>
       <c r="M53">
-        <v>3.045006</v>
+        <v>3.104712</v>
       </c>
       <c r="N53">
-        <v>23.614994</v>
+        <v>23.555288</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>23.614994</v>
+        <v>23.555288</v>
       </c>
       <c r="Q53">
-        <v>24.454994</v>
+        <v>24.395288</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1488487560377807</v>
+        <v>0.1509956051219011</v>
       </c>
       <c r="T53">
-        <v>2.008612059725094</v>
+        <v>2.0504581443027</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5879,7 +5879,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>8.755319365544764</v>
+        <v>8.586947839284289</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5887,22 +5887,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1002978904585125</v>
+        <v>0.1003748904585125</v>
       </c>
       <c r="C54">
-        <v>51.74278490463158</v>
+        <v>50.56515125204887</v>
       </c>
       <c r="D54">
-        <v>95.47478490463158</v>
+        <v>95.41315125204888</v>
       </c>
       <c r="E54">
-        <v>47.032</v>
+        <v>48.148</v>
       </c>
       <c r="F54">
-        <v>58.032</v>
+        <v>59.148</v>
       </c>
       <c r="G54">
         <v>14.3</v>
@@ -5923,28 +5923,28 @@
         <v>26.66</v>
       </c>
       <c r="M54">
-        <v>3.104712</v>
+        <v>3.164418</v>
       </c>
       <c r="N54">
-        <v>23.555288</v>
+        <v>23.495582</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
       <c r="P54">
-        <v>23.555288</v>
+        <v>23.495582</v>
       </c>
       <c r="Q54">
-        <v>24.395288</v>
+        <v>24.335582</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1509956051219011</v>
+        <v>0.1532338094861969</v>
       </c>
       <c r="T54">
-        <v>2.0504581443027</v>
+        <v>2.094084913330417</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5961,7 +5961,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>8.586947839284289</v>
+        <v>8.424929955524206</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5969,22 +5969,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1003748904585125</v>
+        <v>0.1004518904585125</v>
       </c>
       <c r="C55">
-        <v>50.56515125204887</v>
+        <v>49.38759712321615</v>
       </c>
       <c r="D55">
-        <v>95.41315125204888</v>
+        <v>95.35159712321615</v>
       </c>
       <c r="E55">
-        <v>48.148</v>
+        <v>49.264</v>
       </c>
       <c r="F55">
-        <v>59.148</v>
+        <v>60.264</v>
       </c>
       <c r="G55">
         <v>14.3</v>
@@ -6005,28 +6005,28 @@
         <v>26.66</v>
       </c>
       <c r="M55">
-        <v>3.164418</v>
+        <v>3.224124</v>
       </c>
       <c r="N55">
-        <v>23.495582</v>
+        <v>23.435876</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>23.495582</v>
+        <v>23.435876</v>
       </c>
       <c r="Q55">
-        <v>24.335582</v>
+        <v>24.275876</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1532338094861969</v>
+        <v>0.1555693270837229</v>
       </c>
       <c r="T55">
-        <v>2.094084913330417</v>
+        <v>2.139608498402817</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.424929955524206</v>
+        <v>8.26891273412561</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6051,22 +6051,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1004518904585125</v>
+        <v>0.1005288904585125</v>
       </c>
       <c r="C56">
-        <v>49.38759712321615</v>
+        <v>48.21012236432251</v>
       </c>
       <c r="D56">
-        <v>95.35159712321615</v>
+        <v>95.29012236432251</v>
       </c>
       <c r="E56">
-        <v>49.264</v>
+        <v>50.38</v>
       </c>
       <c r="F56">
-        <v>60.264</v>
+        <v>61.38</v>
       </c>
       <c r="G56">
         <v>14.3</v>
@@ -6087,28 +6087,28 @@
         <v>26.66</v>
       </c>
       <c r="M56">
-        <v>3.224124</v>
+        <v>3.28383</v>
       </c>
       <c r="N56">
-        <v>23.435876</v>
+        <v>23.37617</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>23.435876</v>
+        <v>23.37617</v>
       </c>
       <c r="Q56">
-        <v>24.275876</v>
+        <v>24.21617</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1555693270837229</v>
+        <v>0.1580086454633612</v>
       </c>
       <c r="T56">
-        <v>2.139608498402817</v>
+        <v>2.18715535392288</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.26891273412561</v>
+        <v>8.118568866232419</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6133,22 +6133,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1005288904585125</v>
+        <v>0.1006058904585125</v>
       </c>
       <c r="C57">
-        <v>48.21012236432251</v>
+        <v>47.03272682195355</v>
       </c>
       <c r="D57">
-        <v>95.29012236432251</v>
+        <v>95.22872682195356</v>
       </c>
       <c r="E57">
-        <v>50.38</v>
+        <v>51.496</v>
       </c>
       <c r="F57">
-        <v>61.38</v>
+        <v>62.496</v>
       </c>
       <c r="G57">
         <v>14.3</v>
@@ -6169,28 +6169,28 @@
         <v>26.66</v>
       </c>
       <c r="M57">
-        <v>3.28383</v>
+        <v>3.343536</v>
       </c>
       <c r="N57">
-        <v>23.37617</v>
+        <v>23.316464</v>
       </c>
       <c r="O57">
         <v>0</v>
       </c>
       <c r="P57">
-        <v>23.37617</v>
+        <v>23.316464</v>
       </c>
       <c r="Q57">
-        <v>24.21617</v>
+        <v>24.156464</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1580086454633612</v>
+        <v>0.1605588419511648</v>
       </c>
       <c r="T57">
-        <v>2.18715535392288</v>
+        <v>2.2368634301484</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.118568866232419</v>
+        <v>7.973594422192553</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1006058904585125</v>
+        <v>0.1006828904585125</v>
       </c>
       <c r="C58">
-        <v>47.03272682195355</v>
+        <v>45.85541034308992</v>
       </c>
       <c r="D58">
-        <v>95.22872682195356</v>
+        <v>95.16741034308993</v>
       </c>
       <c r="E58">
-        <v>51.496</v>
+        <v>52.612</v>
       </c>
       <c r="F58">
-        <v>62.496</v>
+        <v>63.612</v>
       </c>
       <c r="G58">
         <v>14.3</v>
@@ -6251,28 +6251,28 @@
         <v>26.66</v>
       </c>
       <c r="M58">
-        <v>3.343536</v>
+        <v>3.403242</v>
       </c>
       <c r="N58">
-        <v>23.316464</v>
+        <v>23.256758</v>
       </c>
       <c r="O58">
         <v>0</v>
       </c>
       <c r="P58">
-        <v>23.316464</v>
+        <v>23.256758</v>
       </c>
       <c r="Q58">
-        <v>24.156464</v>
+        <v>24.096758</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1605588419511648</v>
+        <v>0.1632276522290989</v>
       </c>
       <c r="T58">
-        <v>2.2368634301484</v>
+        <v>2.288883509919293</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6289,7 +6289,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>7.973594422192553</v>
+        <v>7.833706800750579</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6297,22 +6297,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1006828904585125</v>
+        <v>0.1007598904585125</v>
       </c>
       <c r="C59">
-        <v>45.85541034308992</v>
+        <v>44.67817277510618</v>
       </c>
       <c r="D59">
-        <v>95.16741034308993</v>
+        <v>95.10617277510619</v>
       </c>
       <c r="E59">
-        <v>52.612</v>
+        <v>53.72800000000001</v>
       </c>
       <c r="F59">
-        <v>63.612</v>
+        <v>64.72800000000001</v>
       </c>
       <c r="G59">
         <v>14.3</v>
@@ -6333,28 +6333,28 @@
         <v>26.66</v>
       </c>
       <c r="M59">
-        <v>3.403242</v>
+        <v>3.462948</v>
       </c>
       <c r="N59">
-        <v>23.256758</v>
+        <v>23.197052</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>23.256758</v>
+        <v>23.197052</v>
       </c>
       <c r="Q59">
-        <v>24.096758</v>
+        <v>24.037052</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1632276522290989</v>
+        <v>0.1660235487107441</v>
       </c>
       <c r="T59">
-        <v>2.288883509919293</v>
+        <v>2.343380736345943</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6371,7 +6371,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>7.833706800750579</v>
+        <v>7.698642890392809</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6379,22 +6379,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1007598904585125</v>
+        <v>0.1013088904585125</v>
       </c>
       <c r="C60">
-        <v>44.67817277510619</v>
+        <v>43.12783052513343</v>
       </c>
       <c r="D60">
-        <v>95.10617277510619</v>
+        <v>94.67183052513343</v>
       </c>
       <c r="E60">
-        <v>53.72799999999999</v>
+        <v>54.84399999999999</v>
       </c>
       <c r="F60">
-        <v>64.72799999999999</v>
+        <v>65.84399999999999</v>
       </c>
       <c r="G60">
         <v>14.3</v>
@@ -6415,45 +6415,45 @@
         <v>26.66</v>
       </c>
       <c r="M60">
-        <v>3.462947999999999</v>
+        <v>3.5753292</v>
       </c>
       <c r="N60">
-        <v>23.197052</v>
+        <v>23.0846708</v>
       </c>
       <c r="O60">
         <v>0</v>
       </c>
       <c r="P60">
-        <v>23.197052</v>
+        <v>23.0846708</v>
       </c>
       <c r="Q60">
-        <v>24.037052</v>
+        <v>23.9246708</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1660235487107441</v>
+        <v>0.1689558303866159</v>
       </c>
       <c r="T60">
-        <v>2.343380736345942</v>
+        <v>2.400536364061697</v>
       </c>
       <c r="U60">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V60">
         <v>0</v>
       </c>
       <c r="W60">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y60">
-        <v>7.698642890392811</v>
+        <v>7.456656019255514</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6461,22 +6461,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1013088904585125</v>
+        <v>0.1013938904585125</v>
       </c>
       <c r="C61">
-        <v>43.12783052513343</v>
+        <v>41.94493705069142</v>
       </c>
       <c r="D61">
-        <v>94.67183052513343</v>
+        <v>94.60493705069142</v>
       </c>
       <c r="E61">
-        <v>54.84399999999999</v>
+        <v>55.95999999999999</v>
       </c>
       <c r="F61">
-        <v>65.84399999999999</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="G61">
         <v>14.3</v>
@@ -6497,28 +6497,28 @@
         <v>26.66</v>
       </c>
       <c r="M61">
-        <v>3.5753292</v>
+        <v>3.635928</v>
       </c>
       <c r="N61">
-        <v>23.0846708</v>
+        <v>23.024072</v>
       </c>
       <c r="O61">
         <v>0</v>
       </c>
       <c r="P61">
-        <v>23.0846708</v>
+        <v>23.024072</v>
       </c>
       <c r="Q61">
-        <v>23.9246708</v>
+        <v>23.864072</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1689558303866159</v>
+        <v>0.1720347261462813</v>
       </c>
       <c r="T61">
-        <v>2.400536364061697</v>
+        <v>2.46054977316324</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>7.456656019255514</v>
+        <v>7.332378418934589</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6543,22 +6543,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1013938904585125</v>
+        <v>0.1014788904585125</v>
       </c>
       <c r="C62">
-        <v>41.94493705069142</v>
+        <v>40.76213804104134</v>
       </c>
       <c r="D62">
-        <v>94.60493705069142</v>
+        <v>94.53813804104134</v>
       </c>
       <c r="E62">
-        <v>55.95999999999999</v>
+        <v>57.07599999999999</v>
       </c>
       <c r="F62">
-        <v>66.95999999999999</v>
+        <v>68.07599999999999</v>
       </c>
       <c r="G62">
         <v>14.3</v>
@@ -6579,28 +6579,28 @@
         <v>26.66</v>
       </c>
       <c r="M62">
-        <v>3.635928</v>
+        <v>3.6965268</v>
       </c>
       <c r="N62">
-        <v>23.024072</v>
+        <v>22.9634732</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>23.024072</v>
+        <v>22.9634732</v>
       </c>
       <c r="Q62">
-        <v>23.864072</v>
+        <v>23.8034732</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1720347261462813</v>
+        <v>0.175271513996186</v>
       </c>
       <c r="T62">
-        <v>2.46054977316324</v>
+        <v>2.523640792987938</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>7.332378418934589</v>
+        <v>7.212175494034022</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6625,22 +6625,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1014788904585125</v>
+        <v>0.1015638904585125</v>
       </c>
       <c r="C63">
-        <v>40.76213804104134</v>
+        <v>39.57943329622412</v>
       </c>
       <c r="D63">
-        <v>94.53813804104134</v>
+        <v>94.47143329622412</v>
       </c>
       <c r="E63">
-        <v>57.07599999999999</v>
+        <v>58.19199999999999</v>
       </c>
       <c r="F63">
-        <v>68.07599999999999</v>
+        <v>69.19199999999999</v>
       </c>
       <c r="G63">
         <v>14.3</v>
@@ -6661,28 +6661,28 @@
         <v>26.66</v>
       </c>
       <c r="M63">
-        <v>3.6965268</v>
+        <v>3.7571256</v>
       </c>
       <c r="N63">
-        <v>22.9634732</v>
+        <v>22.9028744</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63">
-        <v>22.9634732</v>
+        <v>22.9028744</v>
       </c>
       <c r="Q63">
-        <v>23.8034732</v>
+        <v>23.7428744</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.175271513996186</v>
+        <v>0.1786786591013488</v>
       </c>
       <c r="T63">
-        <v>2.523640792987938</v>
+        <v>2.59005239280341</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>7.212175494034022</v>
+        <v>7.095850082839925</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6707,22 +6707,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1015638904585125</v>
+        <v>0.1016488904585125</v>
       </c>
       <c r="C64">
-        <v>39.57943329622412</v>
+        <v>38.3968226168448</v>
       </c>
       <c r="D64">
-        <v>94.47143329622412</v>
+        <v>94.4048226168448</v>
       </c>
       <c r="E64">
-        <v>58.19199999999999</v>
+        <v>59.30799999999999</v>
       </c>
       <c r="F64">
-        <v>69.19199999999999</v>
+        <v>70.30799999999999</v>
       </c>
       <c r="G64">
         <v>14.3</v>
@@ -6743,28 +6743,28 @@
         <v>26.66</v>
       </c>
       <c r="M64">
-        <v>3.7571256</v>
+        <v>3.817724399999999</v>
       </c>
       <c r="N64">
-        <v>22.9028744</v>
+        <v>22.8422756</v>
       </c>
       <c r="O64">
         <v>0</v>
       </c>
       <c r="P64">
-        <v>22.9028744</v>
+        <v>22.8422756</v>
       </c>
       <c r="Q64">
-        <v>23.7428744</v>
+        <v>23.6822756</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1786786591013488</v>
+        <v>0.182269974212196</v>
       </c>
       <c r="T64">
-        <v>2.59005239280341</v>
+        <v>2.660053808825124</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6781,7 +6781,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>7.095850082839925</v>
+        <v>6.983217541842466</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6789,22 +6789,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1016488904585125</v>
+        <v>0.1017338904585125</v>
       </c>
       <c r="C65">
-        <v>38.3968226168448</v>
+        <v>37.21430580407031</v>
       </c>
       <c r="D65">
-        <v>94.4048226168448</v>
+        <v>94.3383058040703</v>
       </c>
       <c r="E65">
-        <v>59.30799999999999</v>
+        <v>60.42399999999999</v>
       </c>
       <c r="F65">
-        <v>70.30799999999999</v>
+        <v>71.42399999999999</v>
       </c>
       <c r="G65">
         <v>14.3</v>
@@ -6825,28 +6825,28 @@
         <v>26.66</v>
       </c>
       <c r="M65">
-        <v>3.817724399999999</v>
+        <v>3.8783232</v>
       </c>
       <c r="N65">
-        <v>22.8422756</v>
+        <v>22.7816768</v>
       </c>
       <c r="O65">
         <v>0</v>
       </c>
       <c r="P65">
-        <v>22.8422756</v>
+        <v>22.7816768</v>
       </c>
       <c r="Q65">
-        <v>23.6822756</v>
+        <v>23.6216768</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.182269974212196</v>
+        <v>0.1860608068292015</v>
       </c>
       <c r="T65">
-        <v>2.660053808825124</v>
+        <v>2.733944192403599</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6863,7 +6863,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>6.983217541842466</v>
+        <v>6.874104767751177</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6871,22 +6871,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1017338904585125</v>
+        <v>0.1018188904585125</v>
       </c>
       <c r="C66">
-        <v>37.21430580407031</v>
+        <v>36.03188265962756</v>
       </c>
       <c r="D66">
-        <v>94.3383058040703</v>
+        <v>94.27188265962755</v>
       </c>
       <c r="E66">
-        <v>60.42399999999999</v>
+        <v>61.53999999999999</v>
       </c>
       <c r="F66">
-        <v>71.42399999999999</v>
+        <v>72.53999999999999</v>
       </c>
       <c r="G66">
         <v>14.3</v>
@@ -6907,28 +6907,28 @@
         <v>26.66</v>
       </c>
       <c r="M66">
-        <v>3.8783232</v>
+        <v>3.938922</v>
       </c>
       <c r="N66">
-        <v>22.7816768</v>
+        <v>22.721078</v>
       </c>
       <c r="O66">
         <v>0</v>
       </c>
       <c r="P66">
-        <v>22.7816768</v>
+        <v>22.721078</v>
       </c>
       <c r="Q66">
-        <v>23.6216768</v>
+        <v>23.561078</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1860608068292015</v>
+        <v>0.190068258452893</v>
       </c>
       <c r="T66">
-        <v>2.733944192403599</v>
+        <v>2.812056883615132</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6945,7 +6945,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>6.874104767751177</v>
+        <v>6.768349309785774</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6953,22 +6953,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1018188904585125</v>
+        <v>0.1019038904585125</v>
       </c>
       <c r="C67">
-        <v>36.03188265962756</v>
+        <v>34.84955298580152</v>
       </c>
       <c r="D67">
-        <v>94.27188265962755</v>
+        <v>94.20555298580153</v>
       </c>
       <c r="E67">
-        <v>61.53999999999999</v>
+        <v>62.65600000000001</v>
       </c>
       <c r="F67">
-        <v>72.53999999999999</v>
+        <v>73.65600000000001</v>
       </c>
       <c r="G67">
         <v>14.3</v>
@@ -6989,28 +6989,28 @@
         <v>26.66</v>
       </c>
       <c r="M67">
-        <v>3.938922</v>
+        <v>3.9995208</v>
       </c>
       <c r="N67">
-        <v>22.721078</v>
+        <v>22.6604792</v>
       </c>
       <c r="O67">
         <v>0</v>
       </c>
       <c r="P67">
-        <v>22.721078</v>
+        <v>22.6604792</v>
       </c>
       <c r="Q67">
-        <v>23.561078</v>
+        <v>23.5004792</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.190068258452893</v>
+        <v>0.1943114425250368</v>
       </c>
       <c r="T67">
-        <v>2.812056883615132</v>
+        <v>2.894764439015576</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>6.768349309785774</v>
+        <v>6.665798562667807</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7035,22 +7035,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1019038904585125</v>
+        <v>0.1019888904585125</v>
       </c>
       <c r="C68">
-        <v>34.84955298580152</v>
+        <v>33.66731658543321</v>
       </c>
       <c r="D68">
-        <v>94.20555298580153</v>
+        <v>94.13931658543322</v>
       </c>
       <c r="E68">
-        <v>62.65600000000001</v>
+        <v>63.77200000000001</v>
       </c>
       <c r="F68">
-        <v>73.65600000000001</v>
+        <v>74.77200000000001</v>
       </c>
       <c r="G68">
         <v>14.3</v>
@@ -7071,28 +7071,28 @@
         <v>26.66</v>
       </c>
       <c r="M68">
-        <v>3.9995208</v>
+        <v>4.0601196</v>
       </c>
       <c r="N68">
-        <v>22.6604792</v>
+        <v>22.5998804</v>
       </c>
       <c r="O68">
         <v>0</v>
       </c>
       <c r="P68">
-        <v>22.6604792</v>
+        <v>22.5998804</v>
       </c>
       <c r="Q68">
-        <v>23.5004792</v>
+        <v>23.4398804</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1943114425250368</v>
+        <v>0.1988117892682198</v>
       </c>
       <c r="T68">
-        <v>2.894764439015576</v>
+        <v>2.9824845735312</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>6.665798562667807</v>
+        <v>6.566309031881721</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7117,22 +7117,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1019888904585125</v>
+        <v>0.1020738904585125</v>
       </c>
       <c r="C69">
-        <v>33.66731658543321</v>
+        <v>32.48517326191774</v>
       </c>
       <c r="D69">
-        <v>94.13931658543322</v>
+        <v>94.07317326191774</v>
       </c>
       <c r="E69">
-        <v>63.77200000000001</v>
+        <v>64.88800000000001</v>
       </c>
       <c r="F69">
-        <v>74.77200000000001</v>
+        <v>75.88800000000001</v>
       </c>
       <c r="G69">
         <v>14.3</v>
@@ -7153,28 +7153,28 @@
         <v>26.66</v>
       </c>
       <c r="M69">
-        <v>4.0601196</v>
+        <v>4.1207184</v>
       </c>
       <c r="N69">
-        <v>22.5998804</v>
+        <v>22.5392816</v>
       </c>
       <c r="O69">
         <v>0</v>
       </c>
       <c r="P69">
-        <v>22.5998804</v>
+        <v>22.5392816</v>
       </c>
       <c r="Q69">
-        <v>23.4398804</v>
+        <v>23.3792816</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1988117892682198</v>
+        <v>0.2035934076828517</v>
       </c>
       <c r="T69">
-        <v>2.9824845735312</v>
+        <v>3.07568721645405</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -7191,7 +7191,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.566309031881721</v>
+        <v>6.469745663765813</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7199,22 +7199,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1020738904585125</v>
+        <v>0.1021588904585125</v>
       </c>
       <c r="C70">
-        <v>32.48517326191774</v>
+        <v>31.3031228192024</v>
       </c>
       <c r="D70">
-        <v>94.07317326191774</v>
+        <v>94.00712281920241</v>
       </c>
       <c r="E70">
-        <v>64.88800000000001</v>
+        <v>66.004</v>
       </c>
       <c r="F70">
-        <v>75.88800000000001</v>
+        <v>77.004</v>
       </c>
       <c r="G70">
         <v>14.3</v>
@@ -7235,28 +7235,28 @@
         <v>26.66</v>
       </c>
       <c r="M70">
-        <v>4.1207184</v>
+        <v>4.181317200000001</v>
       </c>
       <c r="N70">
-        <v>22.5392816</v>
+        <v>22.4786828</v>
       </c>
       <c r="O70">
         <v>0</v>
       </c>
       <c r="P70">
-        <v>22.5392816</v>
+        <v>22.4786828</v>
       </c>
       <c r="Q70">
-        <v>23.3792816</v>
+        <v>23.3186828</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2035934076828517</v>
+        <v>0.208683517608105</v>
       </c>
       <c r="T70">
-        <v>3.07568721645405</v>
+        <v>3.174902933113859</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7273,7 +7273,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.469745663765813</v>
+        <v>6.375981233856163</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7281,22 +7281,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1021588904585125</v>
+        <v>0.1022438904585125</v>
       </c>
       <c r="C71">
-        <v>31.3031228192024</v>
+        <v>30.12116506178467</v>
       </c>
       <c r="D71">
-        <v>94.00712281920241</v>
+        <v>93.94116506178467</v>
       </c>
       <c r="E71">
-        <v>66.004</v>
+        <v>67.12</v>
       </c>
       <c r="F71">
-        <v>77.004</v>
+        <v>78.12</v>
       </c>
       <c r="G71">
         <v>14.3</v>
@@ -7317,28 +7317,28 @@
         <v>26.66</v>
       </c>
       <c r="M71">
-        <v>4.181317200000001</v>
+        <v>4.241916000000001</v>
       </c>
       <c r="N71">
-        <v>22.4786828</v>
+        <v>22.418084</v>
       </c>
       <c r="O71">
         <v>0</v>
       </c>
       <c r="P71">
-        <v>22.4786828</v>
+        <v>22.418084</v>
       </c>
       <c r="Q71">
-        <v>23.3186828</v>
+        <v>23.258084</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.208683517608105</v>
+        <v>0.2141129681950418</v>
       </c>
       <c r="T71">
-        <v>3.174902933113859</v>
+        <v>3.28073303088432</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7355,7 +7355,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.375981233856163</v>
+        <v>6.284895787658217</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7363,22 +7363,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1022438904585125</v>
+        <v>0.1023288904585125</v>
       </c>
       <c r="C72">
-        <v>30.12116506178467</v>
+        <v>28.93929979471029</v>
       </c>
       <c r="D72">
-        <v>93.94116506178467</v>
+        <v>93.8752997947103</v>
       </c>
       <c r="E72">
-        <v>67.12</v>
+        <v>68.236</v>
       </c>
       <c r="F72">
-        <v>78.12</v>
+        <v>79.236</v>
       </c>
       <c r="G72">
         <v>14.3</v>
@@ -7399,28 +7399,28 @@
         <v>26.66</v>
       </c>
       <c r="M72">
-        <v>4.241916000000001</v>
+        <v>4.3025148</v>
       </c>
       <c r="N72">
-        <v>22.418084</v>
+        <v>22.3574852</v>
       </c>
       <c r="O72">
         <v>0</v>
       </c>
       <c r="P72">
-        <v>22.418084</v>
+        <v>22.3574852</v>
       </c>
       <c r="Q72">
-        <v>23.258084</v>
+        <v>23.1974852</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2141129681950418</v>
+        <v>0.2199168636500433</v>
       </c>
       <c r="T72">
-        <v>3.28073303088432</v>
+        <v>3.393861756087228</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.284895787658217</v>
+        <v>6.196376128677117</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7445,22 +7445,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1023288904585125</v>
+        <v>0.1031338904585125</v>
       </c>
       <c r="C73">
-        <v>28.93929979471031</v>
+        <v>27.20406612653362</v>
       </c>
       <c r="D73">
-        <v>93.8752997947103</v>
+        <v>93.25606612653361</v>
       </c>
       <c r="E73">
-        <v>68.23599999999999</v>
+        <v>69.35199999999999</v>
       </c>
       <c r="F73">
-        <v>79.23599999999999</v>
+        <v>80.35199999999999</v>
       </c>
       <c r="G73">
         <v>14.3</v>
@@ -7481,45 +7481,45 @@
         <v>26.66</v>
       </c>
       <c r="M73">
-        <v>4.3025148</v>
+        <v>4.4434656</v>
       </c>
       <c r="N73">
-        <v>22.3574852</v>
+        <v>22.2165344</v>
       </c>
       <c r="O73">
         <v>0</v>
       </c>
       <c r="P73">
-        <v>22.3574852</v>
+        <v>22.2165344</v>
       </c>
       <c r="Q73">
-        <v>23.1974852</v>
+        <v>23.0565344</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2199168636500432</v>
+        <v>0.2261353230661162</v>
       </c>
       <c r="T73">
-        <v>3.393861756087227</v>
+        <v>3.515071104518914</v>
       </c>
       <c r="U73">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V73">
         <v>0</v>
       </c>
       <c r="W73">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y73">
-        <v>6.196376128677117</v>
+        <v>5.999821400665283</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7527,22 +7527,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1031338904585125</v>
+        <v>0.1032288904585125</v>
       </c>
       <c r="C74">
-        <v>27.20406612653362</v>
+        <v>26.01552737186812</v>
       </c>
       <c r="D74">
-        <v>93.25606612653361</v>
+        <v>93.18352737186811</v>
       </c>
       <c r="E74">
-        <v>69.35199999999999</v>
+        <v>70.46799999999999</v>
       </c>
       <c r="F74">
-        <v>80.35199999999999</v>
+        <v>81.46799999999999</v>
       </c>
       <c r="G74">
         <v>14.3</v>
@@ -7563,28 +7563,28 @@
         <v>26.66</v>
       </c>
       <c r="M74">
-        <v>4.4434656</v>
+        <v>4.5051804</v>
       </c>
       <c r="N74">
-        <v>22.2165344</v>
+        <v>22.1548196</v>
       </c>
       <c r="O74">
         <v>0</v>
       </c>
       <c r="P74">
-        <v>22.2165344</v>
+        <v>22.1548196</v>
       </c>
       <c r="Q74">
-        <v>23.0565344</v>
+        <v>22.9948196</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2261353230661162</v>
+        <v>0.2328144091056019</v>
       </c>
       <c r="T74">
-        <v>3.515071104518914</v>
+        <v>3.645258923204799</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7601,7 +7601,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.999821400665283</v>
+        <v>5.917632066409594</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7609,22 +7609,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1032288904585125</v>
+        <v>0.1033238904585125</v>
       </c>
       <c r="C75">
-        <v>26.01552737186812</v>
+        <v>24.82710137729231</v>
       </c>
       <c r="D75">
-        <v>93.18352737186811</v>
+        <v>93.1111013772923</v>
       </c>
       <c r="E75">
-        <v>70.46799999999999</v>
+        <v>71.58399999999999</v>
       </c>
       <c r="F75">
-        <v>81.46799999999999</v>
+        <v>82.58399999999999</v>
       </c>
       <c r="G75">
         <v>14.3</v>
@@ -7645,28 +7645,28 @@
         <v>26.66</v>
       </c>
       <c r="M75">
-        <v>4.5051804</v>
+        <v>4.566895199999999</v>
       </c>
       <c r="N75">
-        <v>22.1548196</v>
+        <v>22.0931048</v>
       </c>
       <c r="O75">
         <v>0</v>
       </c>
       <c r="P75">
-        <v>22.1548196</v>
+        <v>22.0931048</v>
       </c>
       <c r="Q75">
-        <v>22.9948196</v>
+        <v>22.9331048</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2328144091056019</v>
+        <v>0.2400072709942789</v>
       </c>
       <c r="T75">
-        <v>3.645258923204799</v>
+        <v>3.785461189481907</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.917632066409594</v>
+        <v>5.837664065512167</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7691,22 +7691,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1033238904585125</v>
+        <v>0.1034188904585125</v>
       </c>
       <c r="C76">
-        <v>24.82710137729231</v>
+        <v>23.63878788008532</v>
       </c>
       <c r="D76">
-        <v>93.1111013772923</v>
+        <v>93.03878788008531</v>
       </c>
       <c r="E76">
-        <v>71.58399999999999</v>
+        <v>72.69999999999999</v>
       </c>
       <c r="F76">
-        <v>82.58399999999999</v>
+        <v>83.69999999999999</v>
       </c>
       <c r="G76">
         <v>14.3</v>
@@ -7727,28 +7727,28 @@
         <v>26.66</v>
       </c>
       <c r="M76">
-        <v>4.566895199999999</v>
+        <v>4.628609999999999</v>
       </c>
       <c r="N76">
-        <v>22.0931048</v>
+        <v>22.03139</v>
       </c>
       <c r="O76">
         <v>0</v>
       </c>
       <c r="P76">
-        <v>22.0931048</v>
+        <v>22.03139</v>
       </c>
       <c r="Q76">
-        <v>22.9331048</v>
+        <v>22.87139</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2400072709942789</v>
+        <v>0.2477755618340501</v>
       </c>
       <c r="T76">
-        <v>3.785461189481907</v>
+        <v>3.936879637061184</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.837664065512167</v>
+        <v>5.759828544638673</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7773,22 +7773,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1034188904585125</v>
+        <v>0.1035138904585125</v>
       </c>
       <c r="C77">
-        <v>23.63878788008532</v>
+        <v>22.45058661834177</v>
       </c>
       <c r="D77">
-        <v>93.03878788008531</v>
+        <v>92.96658661834178</v>
       </c>
       <c r="E77">
-        <v>72.69999999999999</v>
+        <v>73.816</v>
       </c>
       <c r="F77">
-        <v>83.69999999999999</v>
+        <v>84.816</v>
       </c>
       <c r="G77">
         <v>14.3</v>
@@ -7809,28 +7809,28 @@
         <v>26.66</v>
       </c>
       <c r="M77">
-        <v>4.628609999999999</v>
+        <v>4.6903248</v>
       </c>
       <c r="N77">
-        <v>22.03139</v>
+        <v>21.9696752</v>
       </c>
       <c r="O77">
         <v>0</v>
       </c>
       <c r="P77">
-        <v>22.03139</v>
+        <v>21.9696752</v>
       </c>
       <c r="Q77">
-        <v>22.87139</v>
+        <v>22.8096752</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2477755618340501</v>
+        <v>0.2561912102438022</v>
       </c>
       <c r="T77">
-        <v>3.936879637061184</v>
+        <v>4.1009162886054</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7847,7 +7847,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.759828544638673</v>
+        <v>5.684041326946057</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7855,22 +7855,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1035138904585125</v>
+        <v>0.1036088904585125</v>
       </c>
       <c r="C78">
-        <v>22.45058661834177</v>
+        <v>21.26249733096876</v>
       </c>
       <c r="D78">
-        <v>92.96658661834178</v>
+        <v>92.89449733096876</v>
       </c>
       <c r="E78">
-        <v>73.816</v>
+        <v>74.932</v>
       </c>
       <c r="F78">
-        <v>84.816</v>
+        <v>85.932</v>
       </c>
       <c r="G78">
         <v>14.3</v>
@@ -7891,28 +7891,28 @@
         <v>26.66</v>
       </c>
       <c r="M78">
-        <v>4.6903248</v>
+        <v>4.752039600000001</v>
       </c>
       <c r="N78">
-        <v>21.9696752</v>
+        <v>21.9079604</v>
       </c>
       <c r="O78">
         <v>0</v>
       </c>
       <c r="P78">
-        <v>21.9696752</v>
+        <v>21.9079604</v>
       </c>
       <c r="Q78">
-        <v>22.8096752</v>
+        <v>22.7479604</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2561912102438022</v>
+        <v>0.2653386541674457</v>
       </c>
       <c r="T78">
-        <v>4.1009162886054</v>
+        <v>4.279216996805634</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.684041326946057</v>
+        <v>5.61022260841429</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7937,22 +7937,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1036088904585125</v>
+        <v>0.1037038904585125</v>
       </c>
       <c r="C79">
-        <v>21.26249733096876</v>
+        <v>20.07451975768242</v>
       </c>
       <c r="D79">
-        <v>92.89449733096876</v>
+        <v>92.82251975768243</v>
       </c>
       <c r="E79">
-        <v>74.932</v>
+        <v>76.048</v>
       </c>
       <c r="F79">
-        <v>85.932</v>
+        <v>87.048</v>
       </c>
       <c r="G79">
         <v>14.3</v>
@@ -7973,28 +7973,28 @@
         <v>26.66</v>
       </c>
       <c r="M79">
-        <v>4.752039600000001</v>
+        <v>4.813754400000001</v>
       </c>
       <c r="N79">
-        <v>21.9079604</v>
+        <v>21.8462456</v>
       </c>
       <c r="O79">
         <v>0</v>
       </c>
       <c r="P79">
-        <v>21.9079604</v>
+        <v>21.8462456</v>
       </c>
       <c r="Q79">
-        <v>22.7479604</v>
+        <v>22.6862456</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2653386541674457</v>
+        <v>0.2753176839023297</v>
       </c>
       <c r="T79">
-        <v>4.279216996805634</v>
+        <v>4.4737268602968</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.61022260841429</v>
+        <v>5.538296677537184</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8019,22 +8019,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1037038904585125</v>
+        <v>0.1037988904585125</v>
       </c>
       <c r="C80">
-        <v>20.07451975768242</v>
+        <v>18.88665363900513</v>
       </c>
       <c r="D80">
-        <v>92.82251975768243</v>
+        <v>92.75065363900514</v>
       </c>
       <c r="E80">
-        <v>76.048</v>
+        <v>77.164</v>
       </c>
       <c r="F80">
-        <v>87.048</v>
+        <v>88.164</v>
       </c>
       <c r="G80">
         <v>14.3</v>
@@ -8055,28 +8055,28 @@
         <v>26.66</v>
       </c>
       <c r="M80">
-        <v>4.813754400000001</v>
+        <v>4.8754692</v>
       </c>
       <c r="N80">
-        <v>21.8462456</v>
+        <v>21.7845308</v>
       </c>
       <c r="O80">
         <v>0</v>
       </c>
       <c r="P80">
-        <v>21.8462456</v>
+        <v>21.7845308</v>
       </c>
       <c r="Q80">
-        <v>22.6862456</v>
+        <v>22.6245308</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2753176839023297</v>
+        <v>0.2862470974214882</v>
       </c>
       <c r="T80">
-        <v>4.4737268602968</v>
+        <v>4.686761472691886</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.538296677537184</v>
+        <v>5.468191656302535</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8101,22 +8101,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1037988904585125</v>
+        <v>0.1038938904585125</v>
       </c>
       <c r="C81">
-        <v>18.88665363900513</v>
+        <v>17.69889871626214</v>
       </c>
       <c r="D81">
-        <v>92.75065363900514</v>
+        <v>92.67889871626214</v>
       </c>
       <c r="E81">
-        <v>77.164</v>
+        <v>78.28</v>
       </c>
       <c r="F81">
-        <v>88.164</v>
+        <v>89.28</v>
       </c>
       <c r="G81">
         <v>14.3</v>
@@ -8137,28 +8137,28 @@
         <v>26.66</v>
       </c>
       <c r="M81">
-        <v>4.8754692</v>
+        <v>4.937184</v>
       </c>
       <c r="N81">
-        <v>21.7845308</v>
+        <v>21.722816</v>
       </c>
       <c r="O81">
         <v>0</v>
       </c>
       <c r="P81">
-        <v>21.7845308</v>
+        <v>21.722816</v>
       </c>
       <c r="Q81">
-        <v>22.6245308</v>
+        <v>22.562816</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2862470974214882</v>
+        <v>0.2982694522925626</v>
       </c>
       <c r="T81">
-        <v>4.686761472691886</v>
+        <v>4.92109954632648</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.468191656302535</v>
+        <v>5.399839260598754</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8183,22 +8183,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1038938904585125</v>
+        <v>0.1039888904585125</v>
       </c>
       <c r="C82">
-        <v>17.69889871626214</v>
+        <v>16.51125473157852</v>
       </c>
       <c r="D82">
-        <v>92.67889871626214</v>
+        <v>92.60725473157852</v>
       </c>
       <c r="E82">
-        <v>78.28</v>
+        <v>79.396</v>
       </c>
       <c r="F82">
-        <v>89.28</v>
+        <v>90.396</v>
       </c>
       <c r="G82">
         <v>14.3</v>
@@ -8219,28 +8219,28 @@
         <v>26.66</v>
       </c>
       <c r="M82">
-        <v>4.937184</v>
+        <v>4.9988988</v>
       </c>
       <c r="N82">
-        <v>21.722816</v>
+        <v>21.6611012</v>
       </c>
       <c r="O82">
         <v>0</v>
       </c>
       <c r="P82">
-        <v>21.722816</v>
+        <v>21.6611012</v>
       </c>
       <c r="Q82">
-        <v>22.562816</v>
+        <v>22.5011012</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2982694522925626</v>
+        <v>0.3115573182026976</v>
       </c>
       <c r="T82">
-        <v>4.92109954632648</v>
+        <v>5.180104785606821</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.399839260598754</v>
+        <v>5.33317457836914</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8265,22 +8265,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1039888904585125</v>
+        <v>0.1040838904585125</v>
       </c>
       <c r="C83">
-        <v>16.51125473157852</v>
+        <v>15.32372142787625</v>
       </c>
       <c r="D83">
-        <v>92.60725473157852</v>
+        <v>92.53572142787625</v>
       </c>
       <c r="E83">
-        <v>79.396</v>
+        <v>80.512</v>
       </c>
       <c r="F83">
-        <v>90.396</v>
+        <v>91.512</v>
       </c>
       <c r="G83">
         <v>14.3</v>
@@ -8301,28 +8301,28 @@
         <v>26.66</v>
       </c>
       <c r="M83">
-        <v>4.9988988</v>
+        <v>5.0606136</v>
       </c>
       <c r="N83">
-        <v>21.6611012</v>
+        <v>21.5993864</v>
       </c>
       <c r="O83">
         <v>0</v>
       </c>
       <c r="P83">
-        <v>21.6611012</v>
+        <v>21.5993864</v>
       </c>
       <c r="Q83">
-        <v>22.5011012</v>
+        <v>22.4393864</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3115573182026976</v>
+        <v>0.326321613658403</v>
       </c>
       <c r="T83">
-        <v>5.180104785606821</v>
+        <v>5.467888384807201</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8339,7 +8339,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.33317457836914</v>
+        <v>5.268135863998785</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8347,22 +8347,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1040838904585125</v>
+        <v>0.1041788904585125</v>
       </c>
       <c r="C84">
-        <v>15.32372142787625</v>
+        <v>14.13629854887083</v>
       </c>
       <c r="D84">
-        <v>92.53572142787625</v>
+        <v>92.46429854887083</v>
       </c>
       <c r="E84">
-        <v>80.512</v>
+        <v>81.628</v>
       </c>
       <c r="F84">
-        <v>91.512</v>
+        <v>92.628</v>
       </c>
       <c r="G84">
         <v>14.3</v>
@@ -8383,28 +8383,28 @@
         <v>26.66</v>
       </c>
       <c r="M84">
-        <v>5.0606136</v>
+        <v>5.1223284</v>
       </c>
       <c r="N84">
-        <v>21.5993864</v>
+        <v>21.5376716</v>
       </c>
       <c r="O84">
         <v>0</v>
       </c>
       <c r="P84">
-        <v>21.5993864</v>
+        <v>21.5376716</v>
       </c>
       <c r="Q84">
-        <v>22.4393864</v>
+        <v>22.3776716</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.326321613658403</v>
+        <v>0.3428228850500738</v>
       </c>
       <c r="T84">
-        <v>5.467888384807201</v>
+        <v>5.789528878031154</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.268135863998785</v>
+        <v>5.204664347565064</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8429,22 +8429,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1041788904585125</v>
+        <v>0.1042738904585125</v>
       </c>
       <c r="C85">
-        <v>14.13629854887083</v>
+        <v>12.94898583906854</v>
       </c>
       <c r="D85">
-        <v>92.46429854887083</v>
+        <v>92.39298583906854</v>
       </c>
       <c r="E85">
-        <v>81.628</v>
+        <v>82.744</v>
       </c>
       <c r="F85">
-        <v>92.628</v>
+        <v>93.744</v>
       </c>
       <c r="G85">
         <v>14.3</v>
@@ -8465,28 +8465,28 @@
         <v>26.66</v>
       </c>
       <c r="M85">
-        <v>5.1223284</v>
+        <v>5.184043200000001</v>
       </c>
       <c r="N85">
-        <v>21.5376716</v>
+        <v>21.4759568</v>
       </c>
       <c r="O85">
         <v>0</v>
       </c>
       <c r="P85">
-        <v>21.5376716</v>
+        <v>21.4759568</v>
       </c>
       <c r="Q85">
-        <v>22.3776716</v>
+        <v>22.3159568</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3428228850500738</v>
+        <v>0.3613868153657034</v>
       </c>
       <c r="T85">
-        <v>5.789528878031154</v>
+        <v>6.151374432908103</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.204664347565064</v>
+        <v>5.142704057713098</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8511,22 +8511,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1042738904585125</v>
+        <v>0.1043688904585125</v>
       </c>
       <c r="C86">
-        <v>12.94898583906856</v>
+        <v>11.76178304376317</v>
       </c>
       <c r="D86">
-        <v>92.39298583906854</v>
+        <v>92.32178304376318</v>
       </c>
       <c r="E86">
-        <v>82.74399999999999</v>
+        <v>83.86</v>
       </c>
       <c r="F86">
-        <v>93.74399999999999</v>
+        <v>94.86</v>
       </c>
       <c r="G86">
         <v>14.3</v>
@@ -8547,28 +8547,28 @@
         <v>26.66</v>
       </c>
       <c r="M86">
-        <v>5.1840432</v>
+        <v>5.245758</v>
       </c>
       <c r="N86">
-        <v>21.4759568</v>
+        <v>21.414242</v>
       </c>
       <c r="O86">
         <v>0</v>
       </c>
       <c r="P86">
-        <v>21.4759568</v>
+        <v>21.414242</v>
       </c>
       <c r="Q86">
-        <v>22.3159568</v>
+        <v>22.254242</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3613868153657032</v>
+        <v>0.3824259363900835</v>
       </c>
       <c r="T86">
-        <v>6.151374432908098</v>
+        <v>6.561466061768638</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8585,7 +8585,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.142704057713099</v>
+        <v>5.082201657034122</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8593,22 +8593,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1043688904585125</v>
+        <v>0.1044638904585125</v>
       </c>
       <c r="C87">
-        <v>11.76178304376317</v>
+        <v>10.57468990903307</v>
       </c>
       <c r="D87">
-        <v>92.32178304376318</v>
+        <v>92.25068990903307</v>
       </c>
       <c r="E87">
-        <v>83.86</v>
+        <v>84.976</v>
       </c>
       <c r="F87">
-        <v>94.86</v>
+        <v>95.976</v>
       </c>
       <c r="G87">
         <v>14.3</v>
@@ -8629,28 +8629,28 @@
         <v>26.66</v>
       </c>
       <c r="M87">
-        <v>5.245758</v>
+        <v>5.3074728</v>
       </c>
       <c r="N87">
-        <v>21.414242</v>
+        <v>21.3525272</v>
       </c>
       <c r="O87">
         <v>0</v>
       </c>
       <c r="P87">
-        <v>21.414242</v>
+        <v>21.3525272</v>
       </c>
       <c r="Q87">
-        <v>22.254242</v>
+        <v>22.1925272</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3824259363900835</v>
+        <v>0.4064706461322323</v>
       </c>
       <c r="T87">
-        <v>6.561466061768638</v>
+        <v>7.030142209037828</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8667,7 +8667,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.082201657034122</v>
+        <v>5.023106288929074</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8675,22 +8675,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1044638904585125</v>
+        <v>0.1045588904585125</v>
       </c>
       <c r="C88">
-        <v>10.57468990903307</v>
+        <v>9.387706181738181</v>
       </c>
       <c r="D88">
-        <v>92.25068990903307</v>
+        <v>92.17970618173818</v>
       </c>
       <c r="E88">
-        <v>84.976</v>
+        <v>86.092</v>
       </c>
       <c r="F88">
-        <v>95.976</v>
+        <v>97.092</v>
       </c>
       <c r="G88">
         <v>14.3</v>
@@ -8711,28 +8711,28 @@
         <v>26.66</v>
       </c>
       <c r="M88">
-        <v>5.3074728</v>
+        <v>5.3691876</v>
       </c>
       <c r="N88">
-        <v>21.3525272</v>
+        <v>21.2908124</v>
       </c>
       <c r="O88">
         <v>0</v>
       </c>
       <c r="P88">
-        <v>21.3525272</v>
+        <v>21.2908124</v>
       </c>
       <c r="Q88">
-        <v>22.1925272</v>
+        <v>22.1308124</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4064706461322323</v>
+        <v>0.4342145419885579</v>
       </c>
       <c r="T88">
-        <v>7.030142209037828</v>
+        <v>7.570922378963814</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8749,7 +8749,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.023106288929074</v>
+        <v>4.965369435033337</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8757,22 +8757,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1045588904585125</v>
+        <v>0.1046538904585125</v>
       </c>
       <c r="C89">
-        <v>9.387706181738181</v>
+        <v>8.200831609516868</v>
       </c>
       <c r="D89">
-        <v>92.17970618173818</v>
+        <v>92.10883160951687</v>
       </c>
       <c r="E89">
-        <v>86.092</v>
+        <v>87.208</v>
       </c>
       <c r="F89">
-        <v>97.092</v>
+        <v>98.208</v>
       </c>
       <c r="G89">
         <v>14.3</v>
@@ -8793,28 +8793,28 @@
         <v>26.66</v>
       </c>
       <c r="M89">
-        <v>5.3691876</v>
+        <v>5.4309024</v>
       </c>
       <c r="N89">
-        <v>21.2908124</v>
+        <v>21.2290976</v>
       </c>
       <c r="O89">
         <v>0</v>
       </c>
       <c r="P89">
-        <v>21.2908124</v>
+        <v>21.2290976</v>
       </c>
       <c r="Q89">
-        <v>22.1308124</v>
+        <v>22.0690976</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4342145419885579</v>
+        <v>0.4665824204876044</v>
       </c>
       <c r="T89">
-        <v>7.570922378963814</v>
+        <v>8.2018325772108</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.965369435033337</v>
+        <v>4.908944782362504</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8839,22 +8839,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1046538904585125</v>
+        <v>0.1047488904585125</v>
       </c>
       <c r="C90">
-        <v>8.200831609516868</v>
+        <v>7.014065940783155</v>
       </c>
       <c r="D90">
-        <v>92.10883160951687</v>
+        <v>92.03806594078316</v>
       </c>
       <c r="E90">
-        <v>87.208</v>
+        <v>88.324</v>
       </c>
       <c r="F90">
-        <v>98.208</v>
+        <v>99.324</v>
       </c>
       <c r="G90">
         <v>14.3</v>
@@ -8875,28 +8875,28 @@
         <v>26.66</v>
       </c>
       <c r="M90">
-        <v>5.4309024</v>
+        <v>5.4926172</v>
       </c>
       <c r="N90">
-        <v>21.2290976</v>
+        <v>21.1673828</v>
       </c>
       <c r="O90">
         <v>0</v>
       </c>
       <c r="P90">
-        <v>21.2290976</v>
+        <v>21.1673828</v>
       </c>
       <c r="Q90">
-        <v>22.0690976</v>
+        <v>22.0073828</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4665824204876044</v>
+        <v>0.5048353678046593</v>
       </c>
       <c r="T90">
-        <v>8.2018325772108</v>
+        <v>8.9474537205936</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8913,7 +8913,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.908944782362504</v>
+        <v>4.853788099414611</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8921,22 +8921,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1047488904585125</v>
+        <v>0.1048438904585125</v>
       </c>
       <c r="C91">
-        <v>7.014065940783155</v>
+        <v>5.827408924723557</v>
       </c>
       <c r="D91">
-        <v>92.03806594078316</v>
+        <v>91.96740892472356</v>
       </c>
       <c r="E91">
-        <v>88.324</v>
+        <v>89.44</v>
       </c>
       <c r="F91">
-        <v>99.324</v>
+        <v>100.44</v>
       </c>
       <c r="G91">
         <v>14.3</v>
@@ -8957,28 +8957,28 @@
         <v>26.66</v>
       </c>
       <c r="M91">
-        <v>5.4926172</v>
+        <v>5.554332</v>
       </c>
       <c r="N91">
-        <v>21.1673828</v>
+        <v>21.105668</v>
       </c>
       <c r="O91">
         <v>0</v>
       </c>
       <c r="P91">
-        <v>21.1673828</v>
+        <v>21.105668</v>
       </c>
       <c r="Q91">
-        <v>22.0073828</v>
+        <v>21.945668</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5048353678046593</v>
+        <v>0.5507389045851252</v>
       </c>
       <c r="T91">
-        <v>8.9474537205936</v>
+        <v>9.84219909265296</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.853788099414611</v>
+        <v>4.799857120532225</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9003,22 +9003,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1048438904585125</v>
+        <v>0.1049388904585125</v>
       </c>
       <c r="C92">
-        <v>5.827408924723557</v>
+        <v>4.640860311294176</v>
       </c>
       <c r="D92">
-        <v>91.96740892472356</v>
+        <v>91.89686031129418</v>
       </c>
       <c r="E92">
-        <v>89.44</v>
+        <v>90.556</v>
       </c>
       <c r="F92">
-        <v>100.44</v>
+        <v>101.556</v>
       </c>
       <c r="G92">
         <v>14.3</v>
@@ -9039,28 +9039,28 @@
         <v>26.66</v>
       </c>
       <c r="M92">
-        <v>5.554332</v>
+        <v>5.6160468</v>
       </c>
       <c r="N92">
-        <v>21.105668</v>
+        <v>21.0439532</v>
       </c>
       <c r="O92">
         <v>0</v>
       </c>
       <c r="P92">
-        <v>21.105668</v>
+        <v>21.0439532</v>
       </c>
       <c r="Q92">
-        <v>21.945668</v>
+        <v>21.8839532</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5507389045851252</v>
+        <v>0.606843227316806</v>
       </c>
       <c r="T92">
-        <v>9.84219909265296</v>
+        <v>10.9357767696144</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -9077,7 +9077,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.799857120532225</v>
+        <v>4.747111437889014</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9085,22 +9085,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1049388904585125</v>
+        <v>0.1050338904585125</v>
       </c>
       <c r="C93">
-        <v>4.640860311294176</v>
+        <v>3.454419851217835</v>
       </c>
       <c r="D93">
-        <v>91.89686031129418</v>
+        <v>91.82641985121784</v>
       </c>
       <c r="E93">
-        <v>90.556</v>
+        <v>91.672</v>
       </c>
       <c r="F93">
-        <v>101.556</v>
+        <v>102.672</v>
       </c>
       <c r="G93">
         <v>14.3</v>
@@ -9121,28 +9121,28 @@
         <v>26.66</v>
       </c>
       <c r="M93">
-        <v>5.6160468</v>
+        <v>5.6777616</v>
       </c>
       <c r="N93">
-        <v>21.0439532</v>
+        <v>20.9822384</v>
       </c>
       <c r="O93">
         <v>0</v>
       </c>
       <c r="P93">
-        <v>21.0439532</v>
+        <v>20.9822384</v>
       </c>
       <c r="Q93">
-        <v>21.8839532</v>
+        <v>21.8222384</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.606843227316806</v>
+        <v>0.6769736307314068</v>
       </c>
       <c r="T93">
-        <v>10.9357767696144</v>
+        <v>12.30274886581621</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -9159,7 +9159,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.747111437889014</v>
+        <v>4.695512400520656</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9167,22 +9167,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1050338904585125</v>
+        <v>0.1051288904585125</v>
       </c>
       <c r="C94">
-        <v>3.454419851217835</v>
+        <v>2.268087295981019</v>
       </c>
       <c r="D94">
-        <v>91.82641985121784</v>
+        <v>91.75608729598102</v>
       </c>
       <c r="E94">
-        <v>91.672</v>
+        <v>92.788</v>
       </c>
       <c r="F94">
-        <v>102.672</v>
+        <v>103.788</v>
       </c>
       <c r="G94">
         <v>14.3</v>
@@ -9203,28 +9203,28 @@
         <v>26.66</v>
       </c>
       <c r="M94">
-        <v>5.6777616</v>
+        <v>5.7394764</v>
       </c>
       <c r="N94">
-        <v>20.9822384</v>
+        <v>20.9205236</v>
       </c>
       <c r="O94">
         <v>0</v>
       </c>
       <c r="P94">
-        <v>20.9822384</v>
+        <v>20.9205236</v>
       </c>
       <c r="Q94">
-        <v>21.8222384</v>
+        <v>21.7605236</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6769736307314068</v>
+        <v>0.7671412922644651</v>
       </c>
       <c r="T94">
-        <v>12.30274886581621</v>
+        <v>14.06028441807567</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.695512400520656</v>
+        <v>4.645023019869896</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9249,22 +9249,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1051288904585125</v>
+        <v>0.1052238904585125</v>
       </c>
       <c r="C95">
-        <v>2.268087295981019</v>
+        <v>1.081862397831031</v>
       </c>
       <c r="D95">
-        <v>91.75608729598102</v>
+        <v>91.68586239783103</v>
       </c>
       <c r="E95">
-        <v>92.788</v>
+        <v>93.904</v>
       </c>
       <c r="F95">
-        <v>103.788</v>
+        <v>104.904</v>
       </c>
       <c r="G95">
         <v>14.3</v>
@@ -9285,28 +9285,28 @@
         <v>26.66</v>
       </c>
       <c r="M95">
-        <v>5.7394764</v>
+        <v>5.8011912</v>
       </c>
       <c r="N95">
-        <v>20.9205236</v>
+        <v>20.8588088</v>
       </c>
       <c r="O95">
         <v>0</v>
       </c>
       <c r="P95">
-        <v>20.9205236</v>
+        <v>20.8588088</v>
       </c>
       <c r="Q95">
-        <v>21.7605236</v>
+        <v>21.6988088</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7671412922644651</v>
+        <v>0.8873648409752095</v>
       </c>
       <c r="T95">
-        <v>14.06028441807567</v>
+        <v>16.40366515442161</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9323,7 +9323,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.645023019869896</v>
+        <v>4.595607881360642</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9331,22 +9331,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1052238904585125</v>
+        <v>0.1053188904585125</v>
       </c>
       <c r="C96">
-        <v>1.081862397831031</v>
+        <v>-0.1042550902269852</v>
       </c>
       <c r="D96">
-        <v>91.68586239783103</v>
+        <v>91.61574490977301</v>
       </c>
       <c r="E96">
-        <v>93.904</v>
+        <v>95.02</v>
       </c>
       <c r="F96">
-        <v>104.904</v>
+        <v>106.02</v>
       </c>
       <c r="G96">
         <v>14.3</v>
@@ -9367,28 +9367,28 @@
         <v>26.66</v>
       </c>
       <c r="M96">
-        <v>5.8011912</v>
+        <v>5.862906</v>
       </c>
       <c r="N96">
-        <v>20.8588088</v>
+        <v>20.797094</v>
       </c>
       <c r="O96">
         <v>0</v>
       </c>
       <c r="P96">
-        <v>20.8588088</v>
+        <v>20.797094</v>
       </c>
       <c r="Q96">
-        <v>21.6988088</v>
+        <v>21.637094</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8873648409752095</v>
+        <v>1.055677809170252</v>
       </c>
       <c r="T96">
-        <v>16.40366515442161</v>
+        <v>19.68439818530594</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9405,7 +9405,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.595607881360642</v>
+        <v>4.547233061556846</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9413,22 +9413,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1053188904585125</v>
+        <v>0.1078138904585125</v>
       </c>
       <c r="C97">
-        <v>-0.1042550902269852</v>
+        <v>-3.024122836280469</v>
       </c>
       <c r="D97">
-        <v>91.61574490977301</v>
+        <v>89.81187716371954</v>
       </c>
       <c r="E97">
-        <v>95.02</v>
+        <v>96.13600000000001</v>
       </c>
       <c r="F97">
-        <v>106.02</v>
+        <v>107.136</v>
       </c>
       <c r="G97">
         <v>14.3</v>
@@ -9449,45 +9449,45 @@
         <v>26.66</v>
       </c>
       <c r="M97">
-        <v>5.862906</v>
+        <v>6.192460800000001</v>
       </c>
       <c r="N97">
-        <v>20.797094</v>
+        <v>20.4675392</v>
       </c>
       <c r="O97">
         <v>0</v>
       </c>
       <c r="P97">
-        <v>20.797094</v>
+        <v>20.4675392</v>
       </c>
       <c r="Q97">
-        <v>21.637094</v>
+        <v>21.3075392</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.055677809170252</v>
+        <v>1.308147261462816</v>
       </c>
       <c r="T97">
-        <v>19.68439818530594</v>
+        <v>24.60549773163244</v>
       </c>
       <c r="U97">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V97">
         <v>0</v>
       </c>
       <c r="W97">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y97">
-        <v>4.547233061556846</v>
+        <v>4.305235165961808</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9495,22 +9495,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1078138904585125</v>
+        <v>0.1079338904585125</v>
       </c>
       <c r="C98">
-        <v>-3.024122836280455</v>
+        <v>-4.225093296036107</v>
       </c>
       <c r="D98">
-        <v>89.81187716371954</v>
+        <v>89.72690670396389</v>
       </c>
       <c r="E98">
-        <v>96.136</v>
+        <v>97.252</v>
       </c>
       <c r="F98">
-        <v>107.136</v>
+        <v>108.252</v>
       </c>
       <c r="G98">
         <v>14.3</v>
@@ -9531,28 +9531,28 @@
         <v>26.66</v>
       </c>
       <c r="M98">
-        <v>6.1924608</v>
+        <v>6.2569656</v>
       </c>
       <c r="N98">
-        <v>20.4675392</v>
+        <v>20.4030344</v>
       </c>
       <c r="O98">
         <v>0</v>
       </c>
       <c r="P98">
-        <v>20.4675392</v>
+        <v>20.4030344</v>
       </c>
       <c r="Q98">
-        <v>21.3075392</v>
+        <v>21.2430344</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.308147261462812</v>
+        <v>1.728929681950416</v>
       </c>
       <c r="T98">
-        <v>24.60549773163238</v>
+        <v>32.80733030884317</v>
       </c>
       <c r="U98">
         <v>0.0578</v>
@@ -9569,7 +9569,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.305235165961809</v>
+        <v>4.260851298271481</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9577,22 +9577,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1079338904585125</v>
+        <v>0.1080538904585125</v>
       </c>
       <c r="C99">
-        <v>-4.225093296036107</v>
+        <v>-5.425903127711408</v>
       </c>
       <c r="D99">
-        <v>89.72690670396389</v>
+        <v>89.64209687228859</v>
       </c>
       <c r="E99">
-        <v>97.252</v>
+        <v>98.36799999999999</v>
       </c>
       <c r="F99">
-        <v>108.252</v>
+        <v>109.368</v>
       </c>
       <c r="G99">
         <v>14.3</v>
@@ -9613,28 +9613,28 @@
         <v>26.66</v>
       </c>
       <c r="M99">
-        <v>6.2569656</v>
+        <v>6.3214704</v>
       </c>
       <c r="N99">
-        <v>20.4030344</v>
+        <v>20.3385296</v>
       </c>
       <c r="O99">
         <v>0</v>
       </c>
       <c r="P99">
-        <v>20.4030344</v>
+        <v>20.3385296</v>
       </c>
       <c r="Q99">
-        <v>21.2430344</v>
+        <v>21.1785296</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.728929681950416</v>
+        <v>2.570494522925624</v>
       </c>
       <c r="T99">
-        <v>32.80733030884317</v>
+        <v>49.21099546326475</v>
       </c>
       <c r="U99">
         <v>0.0578</v>
@@ -9651,7 +9651,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.260851298271481</v>
+        <v>4.217373223799324</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9659,22 +9659,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1080538904585125</v>
+        <v>0.1081738904585125</v>
       </c>
       <c r="C100">
-        <v>-5.425903127711408</v>
+        <v>-6.626552786353059</v>
       </c>
       <c r="D100">
-        <v>89.64209687228859</v>
+        <v>89.55744721364694</v>
       </c>
       <c r="E100">
-        <v>98.36799999999999</v>
+        <v>99.48399999999999</v>
       </c>
       <c r="F100">
-        <v>109.368</v>
+        <v>110.484</v>
       </c>
       <c r="G100">
         <v>14.3</v>
@@ -9695,28 +9695,28 @@
         <v>26.66</v>
       </c>
       <c r="M100">
-        <v>6.3214704</v>
+        <v>6.3859752</v>
       </c>
       <c r="N100">
-        <v>20.3385296</v>
+        <v>20.2740248</v>
       </c>
       <c r="O100">
         <v>0</v>
       </c>
       <c r="P100">
-        <v>20.3385296</v>
+        <v>20.2740248</v>
       </c>
       <c r="Q100">
-        <v>21.1785296</v>
+        <v>21.1140248</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.570494522925624</v>
+        <v>5.095189045851248</v>
       </c>
       <c r="T100">
-        <v>49.21099546326475</v>
+        <v>98.4219909265295</v>
       </c>
       <c r="U100">
         <v>0.0578</v>
@@ -9733,91 +9733,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.217373223799324</v>
+        <v>4.174773494265997</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1081738904585125</v>
-      </c>
-      <c r="C101">
-        <v>-6.626552786353059</v>
-      </c>
-      <c r="D101">
-        <v>89.55744721364694</v>
-      </c>
-      <c r="E101">
-        <v>99.48399999999999</v>
-      </c>
-      <c r="F101">
-        <v>110.484</v>
-      </c>
-      <c r="G101">
-        <v>14.3</v>
-      </c>
-      <c r="H101">
-        <v>100.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>27.5</v>
-      </c>
-      <c r="K101">
-        <v>0.84</v>
-      </c>
-      <c r="L101">
-        <v>26.66</v>
-      </c>
-      <c r="M101">
-        <v>6.3859752</v>
-      </c>
-      <c r="N101">
-        <v>20.2740248</v>
-      </c>
-      <c r="O101">
-        <v>0</v>
-      </c>
-      <c r="P101">
-        <v>20.2740248</v>
-      </c>
-      <c r="Q101">
-        <v>21.1140248</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.095189045851248</v>
-      </c>
-      <c r="T101">
-        <v>98.4219909265295</v>
-      </c>
-      <c r="U101">
-        <v>0.0578</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.0578</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Baa2/BBB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.174773494265997</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
